--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M838"/>
+  <dimension ref="A1:M841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36488,6 +36488,135 @@
         <v>14.82</v>
       </c>
       <c r="M838" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>5592</v>
+      </c>
+      <c r="D839" t="n">
+        <v>2436</v>
+      </c>
+      <c r="E839" t="n">
+        <v>730</v>
+      </c>
+      <c r="F839" t="n">
+        <v>230</v>
+      </c>
+      <c r="G839" t="n">
+        <v>1485</v>
+      </c>
+      <c r="H839" t="n">
+        <v>711</v>
+      </c>
+      <c r="I839" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="J839" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="K839" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L839" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="M839" t="n">
+        <v>12.71</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>6059</v>
+      </c>
+      <c r="D840" t="n">
+        <v>4463</v>
+      </c>
+      <c r="E840" t="n">
+        <v>720</v>
+      </c>
+      <c r="F840" t="n">
+        <v>263</v>
+      </c>
+      <c r="G840" t="n">
+        <v>578</v>
+      </c>
+      <c r="H840" t="n">
+        <v>35</v>
+      </c>
+      <c r="I840" t="n">
+        <v>73.66</v>
+      </c>
+      <c r="J840" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="K840" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="L840" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>11609</v>
+      </c>
+      <c r="D841" t="n">
+        <v>7929</v>
+      </c>
+      <c r="E841" t="n">
+        <v>1431</v>
+      </c>
+      <c r="F841" t="n">
+        <v>498</v>
+      </c>
+      <c r="G841" t="n">
+        <v>1751</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="J841" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="K841" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L841" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="M841" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36574,7 +36703,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -36585,39 +36714,39 @@
         <v>5592</v>
       </c>
       <c r="D2" t="n">
-        <v>2590</v>
+        <v>2436</v>
       </c>
       <c r="E2" t="n">
-        <v>566</v>
+        <v>730</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="G2" t="n">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="H2" t="n">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="I2" t="n">
-        <v>46.32</v>
+        <v>43.56</v>
       </c>
       <c r="J2" t="n">
-        <v>10.12</v>
+        <v>13.05</v>
       </c>
       <c r="K2" t="n">
-        <v>4.47</v>
+        <v>4.11</v>
       </c>
       <c r="L2" t="n">
-        <v>26.34</v>
+        <v>26.56</v>
       </c>
       <c r="M2" t="n">
-        <v>12.75</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -36625,42 +36754,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6060</v>
+        <v>6059</v>
       </c>
       <c r="D3" t="n">
-        <v>4652</v>
+        <v>4463</v>
       </c>
       <c r="E3" t="n">
-        <v>520</v>
+        <v>720</v>
       </c>
       <c r="F3" t="n">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="G3" t="n">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" t="n">
-        <v>76.77</v>
+        <v>73.66</v>
       </c>
       <c r="J3" t="n">
-        <v>8.58</v>
+        <v>11.88</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.34</v>
       </c>
       <c r="L3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -36671,31 +36800,31 @@
         <v>11609</v>
       </c>
       <c r="D4" t="n">
-        <v>8233</v>
+        <v>7929</v>
       </c>
       <c r="E4" t="n">
-        <v>1123</v>
+        <v>1431</v>
       </c>
       <c r="F4" t="n">
-        <v>533</v>
+        <v>498</v>
       </c>
       <c r="G4" t="n">
-        <v>1720</v>
+        <v>1751</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.92</v>
+        <v>68.3</v>
       </c>
       <c r="J4" t="n">
-        <v>9.67</v>
+        <v>12.33</v>
       </c>
       <c r="K4" t="n">
-        <v>4.59</v>
+        <v>4.29</v>
       </c>
       <c r="L4" t="n">
-        <v>14.82</v>
+        <v>15.08</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M841"/>
+  <dimension ref="A1:M844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36617,6 +36617,135 @@
         <v>15.08</v>
       </c>
       <c r="M841" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>5592</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2573</v>
+      </c>
+      <c r="E842" t="n">
+        <v>607</v>
+      </c>
+      <c r="F842" t="n">
+        <v>225</v>
+      </c>
+      <c r="G842" t="n">
+        <v>1477</v>
+      </c>
+      <c r="H842" t="n">
+        <v>710</v>
+      </c>
+      <c r="I842" t="n">
+        <v>46.01</v>
+      </c>
+      <c r="J842" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="K842" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L842" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="M842" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>6061</v>
+      </c>
+      <c r="D843" t="n">
+        <v>4339</v>
+      </c>
+      <c r="E843" t="n">
+        <v>843</v>
+      </c>
+      <c r="F843" t="n">
+        <v>269</v>
+      </c>
+      <c r="G843" t="n">
+        <v>575</v>
+      </c>
+      <c r="H843" t="n">
+        <v>35</v>
+      </c>
+      <c r="I843" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="J843" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="K843" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L843" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="M843" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>11611</v>
+      </c>
+      <c r="D844" t="n">
+        <v>7887</v>
+      </c>
+      <c r="E844" t="n">
+        <v>1477</v>
+      </c>
+      <c r="F844" t="n">
+        <v>492</v>
+      </c>
+      <c r="G844" t="n">
+        <v>1755</v>
+      </c>
+      <c r="H844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I844" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="J844" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="K844" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="L844" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="M844" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36703,7 +36832,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -36714,39 +36843,39 @@
         <v>5592</v>
       </c>
       <c r="D2" t="n">
-        <v>2436</v>
+        <v>2573</v>
       </c>
       <c r="E2" t="n">
-        <v>730</v>
+        <v>607</v>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G2" t="n">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="H2" t="n">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I2" t="n">
-        <v>43.56</v>
+        <v>46.01</v>
       </c>
       <c r="J2" t="n">
-        <v>13.05</v>
+        <v>10.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.11</v>
+        <v>4.02</v>
       </c>
       <c r="L2" t="n">
-        <v>26.56</v>
+        <v>26.41</v>
       </c>
       <c r="M2" t="n">
-        <v>12.71</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -36754,34 +36883,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6059</v>
+        <v>6061</v>
       </c>
       <c r="D3" t="n">
-        <v>4463</v>
+        <v>4339</v>
       </c>
       <c r="E3" t="n">
-        <v>720</v>
+        <v>843</v>
       </c>
       <c r="F3" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G3" t="n">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H3" t="n">
         <v>35</v>
       </c>
       <c r="I3" t="n">
-        <v>73.66</v>
+        <v>71.59</v>
       </c>
       <c r="J3" t="n">
-        <v>11.88</v>
+        <v>13.91</v>
       </c>
       <c r="K3" t="n">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
       <c r="L3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="M3" t="n">
         <v>0.58</v>
@@ -36789,7 +36918,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -36797,34 +36926,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11609</v>
+        <v>11611</v>
       </c>
       <c r="D4" t="n">
-        <v>7929</v>
+        <v>7887</v>
       </c>
       <c r="E4" t="n">
-        <v>1431</v>
+        <v>1477</v>
       </c>
       <c r="F4" t="n">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="G4" t="n">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.3</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>12.33</v>
+        <v>12.72</v>
       </c>
       <c r="K4" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="L4" t="n">
-        <v>15.08</v>
+        <v>15.11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M844"/>
+  <dimension ref="A1:M847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36746,6 +36746,135 @@
         <v>15.11</v>
       </c>
       <c r="M844" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>5593</v>
+      </c>
+      <c r="D845" t="n">
+        <v>2655</v>
+      </c>
+      <c r="E845" t="n">
+        <v>533</v>
+      </c>
+      <c r="F845" t="n">
+        <v>242</v>
+      </c>
+      <c r="G845" t="n">
+        <v>1453</v>
+      </c>
+      <c r="H845" t="n">
+        <v>710</v>
+      </c>
+      <c r="I845" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="J845" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="K845" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L845" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="M845" t="n">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>6061</v>
+      </c>
+      <c r="D846" t="n">
+        <v>4390</v>
+      </c>
+      <c r="E846" t="n">
+        <v>802</v>
+      </c>
+      <c r="F846" t="n">
+        <v>259</v>
+      </c>
+      <c r="G846" t="n">
+        <v>575</v>
+      </c>
+      <c r="H846" t="n">
+        <v>35</v>
+      </c>
+      <c r="I846" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="J846" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="K846" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L846" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="M846" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>11612</v>
+      </c>
+      <c r="D847" t="n">
+        <v>7999</v>
+      </c>
+      <c r="E847" t="n">
+        <v>1374</v>
+      </c>
+      <c r="F847" t="n">
+        <v>495</v>
+      </c>
+      <c r="G847" t="n">
+        <v>1744</v>
+      </c>
+      <c r="H847" t="n">
+        <v>0</v>
+      </c>
+      <c r="I847" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="J847" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="K847" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="L847" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="M847" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36832,7 +36961,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -36840,42 +36969,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5592</v>
+        <v>5593</v>
       </c>
       <c r="D2" t="n">
-        <v>2573</v>
+        <v>2655</v>
       </c>
       <c r="E2" t="n">
-        <v>607</v>
+        <v>533</v>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="G2" t="n">
-        <v>1477</v>
+        <v>1453</v>
       </c>
       <c r="H2" t="n">
         <v>710</v>
       </c>
       <c r="I2" t="n">
-        <v>46.01</v>
+        <v>47.47</v>
       </c>
       <c r="J2" t="n">
-        <v>10.85</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>4.02</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>26.41</v>
+        <v>25.98</v>
       </c>
       <c r="M2" t="n">
-        <v>12.7</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -36886,13 +37015,13 @@
         <v>6061</v>
       </c>
       <c r="D3" t="n">
-        <v>4339</v>
+        <v>4390</v>
       </c>
       <c r="E3" t="n">
-        <v>843</v>
+        <v>802</v>
       </c>
       <c r="F3" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="G3" t="n">
         <v>575</v>
@@ -36901,13 +37030,13 @@
         <v>35</v>
       </c>
       <c r="I3" t="n">
-        <v>71.59</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>13.91</v>
+        <v>13.23</v>
       </c>
       <c r="K3" t="n">
-        <v>4.44</v>
+        <v>4.27</v>
       </c>
       <c r="L3" t="n">
         <v>9.49</v>
@@ -36918,7 +37047,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -36926,34 +37055,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11611</v>
+        <v>11612</v>
       </c>
       <c r="D4" t="n">
-        <v>7887</v>
+        <v>7999</v>
       </c>
       <c r="E4" t="n">
-        <v>1477</v>
+        <v>1374</v>
       </c>
       <c r="F4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G4" t="n">
-        <v>1755</v>
+        <v>1744</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>67.93000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="J4" t="n">
-        <v>12.72</v>
+        <v>11.83</v>
       </c>
       <c r="K4" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="L4" t="n">
-        <v>15.11</v>
+        <v>15.02</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M847"/>
+  <dimension ref="A1:M850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36875,6 +36875,135 @@
         <v>15.02</v>
       </c>
       <c r="M847" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>5562</v>
+      </c>
+      <c r="D848" t="n">
+        <v>2656</v>
+      </c>
+      <c r="E848" t="n">
+        <v>528</v>
+      </c>
+      <c r="F848" t="n">
+        <v>255</v>
+      </c>
+      <c r="G848" t="n">
+        <v>1432</v>
+      </c>
+      <c r="H848" t="n">
+        <v>691</v>
+      </c>
+      <c r="I848" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="J848" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="K848" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="L848" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="M848" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>6061</v>
+      </c>
+      <c r="D849" t="n">
+        <v>4372</v>
+      </c>
+      <c r="E849" t="n">
+        <v>825</v>
+      </c>
+      <c r="F849" t="n">
+        <v>254</v>
+      </c>
+      <c r="G849" t="n">
+        <v>576</v>
+      </c>
+      <c r="H849" t="n">
+        <v>34</v>
+      </c>
+      <c r="I849" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="J849" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="K849" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L849" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M849" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>11582</v>
+      </c>
+      <c r="D850" t="n">
+        <v>7931</v>
+      </c>
+      <c r="E850" t="n">
+        <v>1406</v>
+      </c>
+      <c r="F850" t="n">
+        <v>500</v>
+      </c>
+      <c r="G850" t="n">
+        <v>1745</v>
+      </c>
+      <c r="H850" t="n">
+        <v>0</v>
+      </c>
+      <c r="I850" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="J850" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="K850" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L850" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="M850" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36961,7 +37090,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -36969,42 +37098,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5593</v>
+        <v>5562</v>
       </c>
       <c r="D2" t="n">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="E2" t="n">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F2" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G2" t="n">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="H2" t="n">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="I2" t="n">
-        <v>47.47</v>
+        <v>47.75</v>
       </c>
       <c r="J2" t="n">
-        <v>9.529999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="L2" t="n">
-        <v>25.98</v>
+        <v>25.75</v>
       </c>
       <c r="M2" t="n">
-        <v>12.69</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37015,39 +37144,39 @@
         <v>6061</v>
       </c>
       <c r="D3" t="n">
-        <v>4390</v>
+        <v>4372</v>
       </c>
       <c r="E3" t="n">
-        <v>802</v>
+        <v>825</v>
       </c>
       <c r="F3" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G3" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>72.43000000000001</v>
+        <v>72.13</v>
       </c>
       <c r="J3" t="n">
-        <v>13.23</v>
+        <v>13.61</v>
       </c>
       <c r="K3" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="L3" t="n">
-        <v>9.49</v>
+        <v>9.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37055,34 +37184,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11612</v>
+        <v>11582</v>
       </c>
       <c r="D4" t="n">
-        <v>7999</v>
+        <v>7931</v>
       </c>
       <c r="E4" t="n">
-        <v>1374</v>
+        <v>1406</v>
       </c>
       <c r="F4" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="G4" t="n">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.89</v>
+        <v>68.48</v>
       </c>
       <c r="J4" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="K4" t="n">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="L4" t="n">
-        <v>15.02</v>
+        <v>15.07</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M850"/>
+  <dimension ref="A1:M853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37004,6 +37004,135 @@
         <v>15.07</v>
       </c>
       <c r="M850" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>5563</v>
+      </c>
+      <c r="D851" t="n">
+        <v>2665</v>
+      </c>
+      <c r="E851" t="n">
+        <v>516</v>
+      </c>
+      <c r="F851" t="n">
+        <v>247</v>
+      </c>
+      <c r="G851" t="n">
+        <v>1446</v>
+      </c>
+      <c r="H851" t="n">
+        <v>689</v>
+      </c>
+      <c r="I851" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="J851" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K851" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L851" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="M851" t="n">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>6062</v>
+      </c>
+      <c r="D852" t="n">
+        <v>4285</v>
+      </c>
+      <c r="E852" t="n">
+        <v>916</v>
+      </c>
+      <c r="F852" t="n">
+        <v>249</v>
+      </c>
+      <c r="G852" t="n">
+        <v>578</v>
+      </c>
+      <c r="H852" t="n">
+        <v>34</v>
+      </c>
+      <c r="I852" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="J852" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="K852" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L852" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="M852" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>11584</v>
+      </c>
+      <c r="D853" t="n">
+        <v>7848</v>
+      </c>
+      <c r="E853" t="n">
+        <v>1484</v>
+      </c>
+      <c r="F853" t="n">
+        <v>495</v>
+      </c>
+      <c r="G853" t="n">
+        <v>1757</v>
+      </c>
+      <c r="H853" t="n">
+        <v>0</v>
+      </c>
+      <c r="I853" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="J853" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="K853" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L853" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="M853" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37090,7 +37219,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37098,42 +37227,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5562</v>
+        <v>5563</v>
       </c>
       <c r="D2" t="n">
-        <v>2656</v>
+        <v>2665</v>
       </c>
       <c r="E2" t="n">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="F2" t="n">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G2" t="n">
-        <v>1432</v>
+        <v>1446</v>
       </c>
       <c r="H2" t="n">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I2" t="n">
-        <v>47.75</v>
+        <v>47.91</v>
       </c>
       <c r="J2" t="n">
-        <v>9.49</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="L2" t="n">
-        <v>25.75</v>
+        <v>25.99</v>
       </c>
       <c r="M2" t="n">
-        <v>12.42</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37141,34 +37270,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6061</v>
+        <v>6062</v>
       </c>
       <c r="D3" t="n">
-        <v>4372</v>
+        <v>4285</v>
       </c>
       <c r="E3" t="n">
-        <v>825</v>
+        <v>916</v>
       </c>
       <c r="F3" t="n">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G3" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>72.13</v>
+        <v>70.69</v>
       </c>
       <c r="J3" t="n">
-        <v>13.61</v>
+        <v>15.11</v>
       </c>
       <c r="K3" t="n">
-        <v>4.19</v>
+        <v>4.11</v>
       </c>
       <c r="L3" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37176,7 +37305,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37184,34 +37313,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11582</v>
+        <v>11584</v>
       </c>
       <c r="D4" t="n">
-        <v>7931</v>
+        <v>7848</v>
       </c>
       <c r="E4" t="n">
-        <v>1406</v>
+        <v>1484</v>
       </c>
       <c r="F4" t="n">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G4" t="n">
-        <v>1745</v>
+        <v>1757</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.48</v>
+        <v>67.75</v>
       </c>
       <c r="J4" t="n">
-        <v>12.14</v>
+        <v>12.81</v>
       </c>
       <c r="K4" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="L4" t="n">
-        <v>15.07</v>
+        <v>15.17</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M853"/>
+  <dimension ref="A1:M856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37133,6 +37133,135 @@
         <v>15.17</v>
       </c>
       <c r="M853" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>5561</v>
+      </c>
+      <c r="D854" t="n">
+        <v>2665</v>
+      </c>
+      <c r="E854" t="n">
+        <v>491</v>
+      </c>
+      <c r="F854" t="n">
+        <v>267</v>
+      </c>
+      <c r="G854" t="n">
+        <v>1451</v>
+      </c>
+      <c r="H854" t="n">
+        <v>687</v>
+      </c>
+      <c r="I854" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="J854" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="K854" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L854" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="M854" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>6063</v>
+      </c>
+      <c r="D855" t="n">
+        <v>4558</v>
+      </c>
+      <c r="E855" t="n">
+        <v>654</v>
+      </c>
+      <c r="F855" t="n">
+        <v>236</v>
+      </c>
+      <c r="G855" t="n">
+        <v>581</v>
+      </c>
+      <c r="H855" t="n">
+        <v>34</v>
+      </c>
+      <c r="I855" t="n">
+        <v>75.18000000000001</v>
+      </c>
+      <c r="J855" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="K855" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L855" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="M855" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>11583</v>
+      </c>
+      <c r="D856" t="n">
+        <v>8126</v>
+      </c>
+      <c r="E856" t="n">
+        <v>1182</v>
+      </c>
+      <c r="F856" t="n">
+        <v>517</v>
+      </c>
+      <c r="G856" t="n">
+        <v>1758</v>
+      </c>
+      <c r="H856" t="n">
+        <v>0</v>
+      </c>
+      <c r="I856" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="J856" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K856" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L856" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="M856" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37219,7 +37348,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37227,42 +37356,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5563</v>
+        <v>5561</v>
       </c>
       <c r="D2" t="n">
         <v>2665</v>
       </c>
       <c r="E2" t="n">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="F2" t="n">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="G2" t="n">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="H2" t="n">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I2" t="n">
-        <v>47.91</v>
+        <v>47.92</v>
       </c>
       <c r="J2" t="n">
-        <v>9.279999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="K2" t="n">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>25.99</v>
+        <v>26.09</v>
       </c>
       <c r="M2" t="n">
-        <v>12.39</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37270,34 +37399,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6062</v>
+        <v>6063</v>
       </c>
       <c r="D3" t="n">
-        <v>4285</v>
+        <v>4558</v>
       </c>
       <c r="E3" t="n">
-        <v>916</v>
+        <v>654</v>
       </c>
       <c r="F3" t="n">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G3" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>70.69</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>15.11</v>
+        <v>10.79</v>
       </c>
       <c r="K3" t="n">
-        <v>4.11</v>
+        <v>3.89</v>
       </c>
       <c r="L3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37305,7 +37434,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37313,34 +37442,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11584</v>
+        <v>11583</v>
       </c>
       <c r="D4" t="n">
-        <v>7848</v>
+        <v>8126</v>
       </c>
       <c r="E4" t="n">
-        <v>1484</v>
+        <v>1182</v>
       </c>
       <c r="F4" t="n">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="G4" t="n">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>67.75</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>12.81</v>
+        <v>10.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.27</v>
+        <v>4.46</v>
       </c>
       <c r="L4" t="n">
-        <v>15.17</v>
+        <v>15.18</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M856"/>
+  <dimension ref="A1:M859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37262,6 +37262,135 @@
         <v>15.18</v>
       </c>
       <c r="M856" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>5561</v>
+      </c>
+      <c r="D857" t="n">
+        <v>2552</v>
+      </c>
+      <c r="E857" t="n">
+        <v>581</v>
+      </c>
+      <c r="F857" t="n">
+        <v>281</v>
+      </c>
+      <c r="G857" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H857" t="n">
+        <v>687</v>
+      </c>
+      <c r="I857" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="J857" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="K857" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="L857" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="M857" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>6062</v>
+      </c>
+      <c r="D858" t="n">
+        <v>4556</v>
+      </c>
+      <c r="E858" t="n">
+        <v>648</v>
+      </c>
+      <c r="F858" t="n">
+        <v>236</v>
+      </c>
+      <c r="G858" t="n">
+        <v>588</v>
+      </c>
+      <c r="H858" t="n">
+        <v>34</v>
+      </c>
+      <c r="I858" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="J858" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="K858" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L858" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M858" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>11582</v>
+      </c>
+      <c r="D859" t="n">
+        <v>8047</v>
+      </c>
+      <c r="E859" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F859" t="n">
+        <v>522</v>
+      </c>
+      <c r="G859" t="n">
+        <v>1778</v>
+      </c>
+      <c r="H859" t="n">
+        <v>0</v>
+      </c>
+      <c r="I859" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="J859" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="K859" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L859" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="M859" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37348,7 +37477,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37359,31 +37488,31 @@
         <v>5561</v>
       </c>
       <c r="D2" t="n">
-        <v>2665</v>
+        <v>2552</v>
       </c>
       <c r="E2" t="n">
-        <v>491</v>
+        <v>581</v>
       </c>
       <c r="F2" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="G2" t="n">
-        <v>1451</v>
+        <v>1460</v>
       </c>
       <c r="H2" t="n">
         <v>687</v>
       </c>
       <c r="I2" t="n">
-        <v>47.92</v>
+        <v>45.89</v>
       </c>
       <c r="J2" t="n">
-        <v>8.83</v>
+        <v>10.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="L2" t="n">
-        <v>26.09</v>
+        <v>26.25</v>
       </c>
       <c r="M2" t="n">
         <v>12.35</v>
@@ -37391,7 +37520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37399,34 +37528,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6063</v>
+        <v>6062</v>
       </c>
       <c r="D3" t="n">
-        <v>4558</v>
+        <v>4556</v>
       </c>
       <c r="E3" t="n">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="F3" t="n">
         <v>236</v>
       </c>
       <c r="G3" t="n">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>75.18000000000001</v>
+        <v>75.16</v>
       </c>
       <c r="J3" t="n">
-        <v>10.79</v>
+        <v>10.69</v>
       </c>
       <c r="K3" t="n">
         <v>3.89</v>
       </c>
       <c r="L3" t="n">
-        <v>9.58</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37434,7 +37563,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37442,34 +37571,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11583</v>
+        <v>11582</v>
       </c>
       <c r="D4" t="n">
-        <v>8126</v>
+        <v>8047</v>
       </c>
       <c r="E4" t="n">
-        <v>1182</v>
+        <v>1235</v>
       </c>
       <c r="F4" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="G4" t="n">
-        <v>1758</v>
+        <v>1778</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.15000000000001</v>
+        <v>69.48</v>
       </c>
       <c r="J4" t="n">
-        <v>10.2</v>
+        <v>10.66</v>
       </c>
       <c r="K4" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="L4" t="n">
-        <v>15.18</v>
+        <v>15.35</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M859"/>
+  <dimension ref="A1:M862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37391,6 +37391,135 @@
         <v>15.35</v>
       </c>
       <c r="M859" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>5561</v>
+      </c>
+      <c r="D860" t="n">
+        <v>2485</v>
+      </c>
+      <c r="E860" t="n">
+        <v>640</v>
+      </c>
+      <c r="F860" t="n">
+        <v>293</v>
+      </c>
+      <c r="G860" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H860" t="n">
+        <v>687</v>
+      </c>
+      <c r="I860" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="J860" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="K860" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="L860" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="M860" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>6062</v>
+      </c>
+      <c r="D861" t="n">
+        <v>4433</v>
+      </c>
+      <c r="E861" t="n">
+        <v>752</v>
+      </c>
+      <c r="F861" t="n">
+        <v>251</v>
+      </c>
+      <c r="G861" t="n">
+        <v>592</v>
+      </c>
+      <c r="H861" t="n">
+        <v>34</v>
+      </c>
+      <c r="I861" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="J861" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="K861" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L861" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M861" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>11582</v>
+      </c>
+      <c r="D862" t="n">
+        <v>7900</v>
+      </c>
+      <c r="E862" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F862" t="n">
+        <v>577</v>
+      </c>
+      <c r="G862" t="n">
+        <v>1785</v>
+      </c>
+      <c r="H862" t="n">
+        <v>0</v>
+      </c>
+      <c r="I862" t="n">
+        <v>68.20999999999999</v>
+      </c>
+      <c r="J862" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K862" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="L862" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="M862" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37477,7 +37606,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37488,31 +37617,31 @@
         <v>5561</v>
       </c>
       <c r="D2" t="n">
-        <v>2552</v>
+        <v>2485</v>
       </c>
       <c r="E2" t="n">
-        <v>581</v>
+        <v>640</v>
       </c>
       <c r="F2" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="G2" t="n">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="H2" t="n">
         <v>687</v>
       </c>
       <c r="I2" t="n">
-        <v>45.89</v>
+        <v>44.69</v>
       </c>
       <c r="J2" t="n">
-        <v>10.45</v>
+        <v>11.51</v>
       </c>
       <c r="K2" t="n">
-        <v>5.05</v>
+        <v>5.27</v>
       </c>
       <c r="L2" t="n">
-        <v>26.25</v>
+        <v>26.18</v>
       </c>
       <c r="M2" t="n">
         <v>12.35</v>
@@ -37520,7 +37649,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37531,31 +37660,31 @@
         <v>6062</v>
       </c>
       <c r="D3" t="n">
-        <v>4556</v>
+        <v>4433</v>
       </c>
       <c r="E3" t="n">
-        <v>648</v>
+        <v>752</v>
       </c>
       <c r="F3" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="G3" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>75.16</v>
+        <v>73.13</v>
       </c>
       <c r="J3" t="n">
-        <v>10.69</v>
+        <v>12.41</v>
       </c>
       <c r="K3" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="L3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37563,7 +37692,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37574,31 +37703,31 @@
         <v>11582</v>
       </c>
       <c r="D4" t="n">
-        <v>8047</v>
+        <v>7900</v>
       </c>
       <c r="E4" t="n">
-        <v>1235</v>
+        <v>1320</v>
       </c>
       <c r="F4" t="n">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="G4" t="n">
-        <v>1778</v>
+        <v>1785</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.48</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>10.66</v>
+        <v>11.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.51</v>
+        <v>4.98</v>
       </c>
       <c r="L4" t="n">
-        <v>15.35</v>
+        <v>15.41</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M862"/>
+  <dimension ref="A1:M865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37520,6 +37520,135 @@
         <v>15.41</v>
       </c>
       <c r="M862" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>5561</v>
+      </c>
+      <c r="D863" t="n">
+        <v>2575</v>
+      </c>
+      <c r="E863" t="n">
+        <v>555</v>
+      </c>
+      <c r="F863" t="n">
+        <v>296</v>
+      </c>
+      <c r="G863" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H863" t="n">
+        <v>687</v>
+      </c>
+      <c r="I863" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="J863" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="K863" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="L863" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="M863" t="n">
+        <v>12.35</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>6060</v>
+      </c>
+      <c r="D864" t="n">
+        <v>4511</v>
+      </c>
+      <c r="E864" t="n">
+        <v>682</v>
+      </c>
+      <c r="F864" t="n">
+        <v>244</v>
+      </c>
+      <c r="G864" t="n">
+        <v>589</v>
+      </c>
+      <c r="H864" t="n">
+        <v>34</v>
+      </c>
+      <c r="I864" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="J864" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K864" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L864" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="M864" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>11580</v>
+      </c>
+      <c r="D865" t="n">
+        <v>8025</v>
+      </c>
+      <c r="E865" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F865" t="n">
+        <v>574</v>
+      </c>
+      <c r="G865" t="n">
+        <v>1777</v>
+      </c>
+      <c r="H865" t="n">
+        <v>0</v>
+      </c>
+      <c r="I865" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="J865" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K865" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="L865" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="M865" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37606,7 +37735,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37617,31 +37746,31 @@
         <v>5561</v>
       </c>
       <c r="D2" t="n">
-        <v>2485</v>
+        <v>2575</v>
       </c>
       <c r="E2" t="n">
-        <v>640</v>
+        <v>555</v>
       </c>
       <c r="F2" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G2" t="n">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="H2" t="n">
         <v>687</v>
       </c>
       <c r="I2" t="n">
-        <v>44.69</v>
+        <v>46.3</v>
       </c>
       <c r="J2" t="n">
-        <v>11.51</v>
+        <v>9.98</v>
       </c>
       <c r="K2" t="n">
-        <v>5.27</v>
+        <v>5.32</v>
       </c>
       <c r="L2" t="n">
-        <v>26.18</v>
+        <v>26.04</v>
       </c>
       <c r="M2" t="n">
         <v>12.35</v>
@@ -37649,7 +37778,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37657,34 +37786,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6062</v>
+        <v>6060</v>
       </c>
       <c r="D3" t="n">
-        <v>4433</v>
+        <v>4511</v>
       </c>
       <c r="E3" t="n">
-        <v>752</v>
+        <v>682</v>
       </c>
       <c r="F3" t="n">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G3" t="n">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>73.13</v>
+        <v>74.44</v>
       </c>
       <c r="J3" t="n">
-        <v>12.41</v>
+        <v>11.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.14</v>
+        <v>4.03</v>
       </c>
       <c r="L3" t="n">
-        <v>9.77</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37692,7 +37821,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37700,34 +37829,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11582</v>
+        <v>11580</v>
       </c>
       <c r="D4" t="n">
-        <v>7900</v>
+        <v>8025</v>
       </c>
       <c r="E4" t="n">
-        <v>1320</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="n">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="G4" t="n">
-        <v>1785</v>
+        <v>1777</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.20999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="J4" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="L4" t="n">
-        <v>15.41</v>
+        <v>15.35</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M865"/>
+  <dimension ref="A1:M868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37649,6 +37649,135 @@
         <v>15.35</v>
       </c>
       <c r="M865" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D866" t="n">
+        <v>2659</v>
+      </c>
+      <c r="E866" t="n">
+        <v>468</v>
+      </c>
+      <c r="F866" t="n">
+        <v>302</v>
+      </c>
+      <c r="G866" t="n">
+        <v>1444</v>
+      </c>
+      <c r="H866" t="n">
+        <v>687</v>
+      </c>
+      <c r="I866" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="J866" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="K866" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="L866" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="M866" t="n">
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>6062</v>
+      </c>
+      <c r="D867" t="n">
+        <v>4533</v>
+      </c>
+      <c r="E867" t="n">
+        <v>637</v>
+      </c>
+      <c r="F867" t="n">
+        <v>268</v>
+      </c>
+      <c r="G867" t="n">
+        <v>590</v>
+      </c>
+      <c r="H867" t="n">
+        <v>34</v>
+      </c>
+      <c r="I867" t="n">
+        <v>74.78</v>
+      </c>
+      <c r="J867" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="K867" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L867" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="M867" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>11581</v>
+      </c>
+      <c r="D868" t="n">
+        <v>8123</v>
+      </c>
+      <c r="E868" t="n">
+        <v>1093</v>
+      </c>
+      <c r="F868" t="n">
+        <v>597</v>
+      </c>
+      <c r="G868" t="n">
+        <v>1768</v>
+      </c>
+      <c r="H868" t="n">
+        <v>0</v>
+      </c>
+      <c r="I868" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="J868" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="K868" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="L868" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="M868" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37735,7 +37864,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37743,42 +37872,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5561</v>
+        <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>2575</v>
+        <v>2659</v>
       </c>
       <c r="E2" t="n">
-        <v>555</v>
+        <v>468</v>
       </c>
       <c r="F2" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G2" t="n">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="H2" t="n">
         <v>687</v>
       </c>
       <c r="I2" t="n">
-        <v>46.3</v>
+        <v>47.82</v>
       </c>
       <c r="J2" t="n">
-        <v>9.98</v>
+        <v>8.42</v>
       </c>
       <c r="K2" t="n">
-        <v>5.32</v>
+        <v>5.43</v>
       </c>
       <c r="L2" t="n">
-        <v>26.04</v>
+        <v>25.97</v>
       </c>
       <c r="M2" t="n">
-        <v>12.35</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37786,34 +37915,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6060</v>
+        <v>6062</v>
       </c>
       <c r="D3" t="n">
-        <v>4511</v>
+        <v>4533</v>
       </c>
       <c r="E3" t="n">
-        <v>682</v>
+        <v>637</v>
       </c>
       <c r="F3" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="G3" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>74.44</v>
+        <v>74.78</v>
       </c>
       <c r="J3" t="n">
-        <v>11.25</v>
+        <v>10.51</v>
       </c>
       <c r="K3" t="n">
-        <v>4.03</v>
+        <v>4.42</v>
       </c>
       <c r="L3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37821,7 +37950,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37829,34 +37958,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11580</v>
+        <v>11581</v>
       </c>
       <c r="D4" t="n">
-        <v>8025</v>
+        <v>8123</v>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1093</v>
       </c>
       <c r="F4" t="n">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="G4" t="n">
-        <v>1777</v>
+        <v>1768</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.3</v>
+        <v>70.14</v>
       </c>
       <c r="J4" t="n">
-        <v>10.4</v>
+        <v>9.44</v>
       </c>
       <c r="K4" t="n">
-        <v>4.96</v>
+        <v>5.15</v>
       </c>
       <c r="L4" t="n">
-        <v>15.35</v>
+        <v>15.27</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M868"/>
+  <dimension ref="A1:M871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37778,6 +37778,135 @@
         <v>15.27</v>
       </c>
       <c r="M868" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D869" t="n">
+        <v>2657</v>
+      </c>
+      <c r="E869" t="n">
+        <v>475</v>
+      </c>
+      <c r="F869" t="n">
+        <v>299</v>
+      </c>
+      <c r="G869" t="n">
+        <v>1443</v>
+      </c>
+      <c r="H869" t="n">
+        <v>686</v>
+      </c>
+      <c r="I869" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="J869" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="K869" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="L869" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="M869" t="n">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>6057</v>
+      </c>
+      <c r="D870" t="n">
+        <v>4394</v>
+      </c>
+      <c r="E870" t="n">
+        <v>764</v>
+      </c>
+      <c r="F870" t="n">
+        <v>273</v>
+      </c>
+      <c r="G870" t="n">
+        <v>592</v>
+      </c>
+      <c r="H870" t="n">
+        <v>34</v>
+      </c>
+      <c r="I870" t="n">
+        <v>72.54000000000001</v>
+      </c>
+      <c r="J870" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="K870" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="L870" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="M870" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>11576</v>
+      </c>
+      <c r="D871" t="n">
+        <v>7963</v>
+      </c>
+      <c r="E871" t="n">
+        <v>1228</v>
+      </c>
+      <c r="F871" t="n">
+        <v>604</v>
+      </c>
+      <c r="G871" t="n">
+        <v>1781</v>
+      </c>
+      <c r="H871" t="n">
+        <v>0</v>
+      </c>
+      <c r="I871" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="J871" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="K871" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="L871" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="M871" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37864,7 +37993,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -37875,39 +38004,39 @@
         <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="E2" t="n">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G2" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="I2" t="n">
-        <v>47.82</v>
+        <v>47.79</v>
       </c>
       <c r="J2" t="n">
-        <v>8.42</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="L2" t="n">
-        <v>25.97</v>
+        <v>25.95</v>
       </c>
       <c r="M2" t="n">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -37915,34 +38044,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6062</v>
+        <v>6057</v>
       </c>
       <c r="D3" t="n">
-        <v>4533</v>
+        <v>4394</v>
       </c>
       <c r="E3" t="n">
-        <v>637</v>
+        <v>764</v>
       </c>
       <c r="F3" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G3" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>74.78</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>10.51</v>
+        <v>12.61</v>
       </c>
       <c r="K3" t="n">
-        <v>4.42</v>
+        <v>4.51</v>
       </c>
       <c r="L3" t="n">
-        <v>9.73</v>
+        <v>9.77</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -37950,7 +38079,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -37958,34 +38087,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11581</v>
+        <v>11576</v>
       </c>
       <c r="D4" t="n">
-        <v>8123</v>
+        <v>7963</v>
       </c>
       <c r="E4" t="n">
-        <v>1093</v>
+        <v>1228</v>
       </c>
       <c r="F4" t="n">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="G4" t="n">
-        <v>1768</v>
+        <v>1781</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.14</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>9.44</v>
+        <v>10.61</v>
       </c>
       <c r="K4" t="n">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="L4" t="n">
-        <v>15.27</v>
+        <v>15.39</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M871"/>
+  <dimension ref="A1:M874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37907,6 +37907,135 @@
         <v>15.39</v>
       </c>
       <c r="M871" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D872" t="n">
+        <v>2596</v>
+      </c>
+      <c r="E872" t="n">
+        <v>537</v>
+      </c>
+      <c r="F872" t="n">
+        <v>304</v>
+      </c>
+      <c r="G872" t="n">
+        <v>1438</v>
+      </c>
+      <c r="H872" t="n">
+        <v>685</v>
+      </c>
+      <c r="I872" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="J872" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="K872" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L872" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="M872" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>6056</v>
+      </c>
+      <c r="D873" t="n">
+        <v>4126</v>
+      </c>
+      <c r="E873" t="n">
+        <v>1019</v>
+      </c>
+      <c r="F873" t="n">
+        <v>266</v>
+      </c>
+      <c r="G873" t="n">
+        <v>611</v>
+      </c>
+      <c r="H873" t="n">
+        <v>34</v>
+      </c>
+      <c r="I873" t="n">
+        <v>68.13</v>
+      </c>
+      <c r="J873" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="K873" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="L873" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="M873" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>11575</v>
+      </c>
+      <c r="D874" t="n">
+        <v>7644</v>
+      </c>
+      <c r="E874" t="n">
+        <v>1519</v>
+      </c>
+      <c r="F874" t="n">
+        <v>602</v>
+      </c>
+      <c r="G874" t="n">
+        <v>1810</v>
+      </c>
+      <c r="H874" t="n">
+        <v>0</v>
+      </c>
+      <c r="I874" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="J874" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="K874" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L874" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="M874" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37993,7 +38122,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38004,39 +38133,39 @@
         <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>2657</v>
+        <v>2596</v>
       </c>
       <c r="E2" t="n">
-        <v>475</v>
+        <v>537</v>
       </c>
       <c r="F2" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G2" t="n">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="H2" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I2" t="n">
-        <v>47.79</v>
+        <v>46.69</v>
       </c>
       <c r="J2" t="n">
-        <v>8.539999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="K2" t="n">
-        <v>5.38</v>
+        <v>5.47</v>
       </c>
       <c r="L2" t="n">
-        <v>25.95</v>
+        <v>25.86</v>
       </c>
       <c r="M2" t="n">
-        <v>12.34</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38044,34 +38173,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6057</v>
+        <v>6056</v>
       </c>
       <c r="D3" t="n">
-        <v>4394</v>
+        <v>4126</v>
       </c>
       <c r="E3" t="n">
-        <v>764</v>
+        <v>1019</v>
       </c>
       <c r="F3" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G3" t="n">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>72.54000000000001</v>
+        <v>68.13</v>
       </c>
       <c r="J3" t="n">
-        <v>12.61</v>
+        <v>16.83</v>
       </c>
       <c r="K3" t="n">
-        <v>4.51</v>
+        <v>4.39</v>
       </c>
       <c r="L3" t="n">
-        <v>9.77</v>
+        <v>10.09</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38079,7 +38208,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38087,34 +38216,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11576</v>
+        <v>11575</v>
       </c>
       <c r="D4" t="n">
-        <v>7963</v>
+        <v>7644</v>
       </c>
       <c r="E4" t="n">
-        <v>1228</v>
+        <v>1519</v>
       </c>
       <c r="F4" t="n">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G4" t="n">
-        <v>1781</v>
+        <v>1810</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.79000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>10.61</v>
+        <v>13.12</v>
       </c>
       <c r="K4" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>15.39</v>
+        <v>15.64</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M874"/>
+  <dimension ref="A1:M877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38036,6 +38036,135 @@
         <v>15.64</v>
       </c>
       <c r="M874" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D875" t="n">
+        <v>2366</v>
+      </c>
+      <c r="E875" t="n">
+        <v>743</v>
+      </c>
+      <c r="F875" t="n">
+        <v>318</v>
+      </c>
+      <c r="G875" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H875" t="n">
+        <v>685</v>
+      </c>
+      <c r="I875" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="J875" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="K875" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="L875" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="M875" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>6055</v>
+      </c>
+      <c r="D876" t="n">
+        <v>4203</v>
+      </c>
+      <c r="E876" t="n">
+        <v>930</v>
+      </c>
+      <c r="F876" t="n">
+        <v>262</v>
+      </c>
+      <c r="G876" t="n">
+        <v>626</v>
+      </c>
+      <c r="H876" t="n">
+        <v>34</v>
+      </c>
+      <c r="I876" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="J876" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="K876" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L876" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="M876" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>11574</v>
+      </c>
+      <c r="D877" t="n">
+        <v>7548</v>
+      </c>
+      <c r="E877" t="n">
+        <v>1589</v>
+      </c>
+      <c r="F877" t="n">
+        <v>605</v>
+      </c>
+      <c r="G877" t="n">
+        <v>1832</v>
+      </c>
+      <c r="H877" t="n">
+        <v>0</v>
+      </c>
+      <c r="I877" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="J877" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="K877" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="L877" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="M877" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38122,7 +38251,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38133,31 +38262,31 @@
         <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>2596</v>
+        <v>2366</v>
       </c>
       <c r="E2" t="n">
-        <v>537</v>
+        <v>743</v>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="G2" t="n">
-        <v>1438</v>
+        <v>1448</v>
       </c>
       <c r="H2" t="n">
         <v>685</v>
       </c>
       <c r="I2" t="n">
-        <v>46.69</v>
+        <v>42.55</v>
       </c>
       <c r="J2" t="n">
-        <v>9.66</v>
+        <v>13.36</v>
       </c>
       <c r="K2" t="n">
-        <v>5.47</v>
+        <v>5.72</v>
       </c>
       <c r="L2" t="n">
-        <v>25.86</v>
+        <v>26.04</v>
       </c>
       <c r="M2" t="n">
         <v>12.32</v>
@@ -38165,7 +38294,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38173,34 +38302,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6056</v>
+        <v>6055</v>
       </c>
       <c r="D3" t="n">
-        <v>4126</v>
+        <v>4203</v>
       </c>
       <c r="E3" t="n">
-        <v>1019</v>
+        <v>930</v>
       </c>
       <c r="F3" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G3" t="n">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>68.13</v>
+        <v>69.41</v>
       </c>
       <c r="J3" t="n">
-        <v>16.83</v>
+        <v>15.36</v>
       </c>
       <c r="K3" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>10.09</v>
+        <v>10.34</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38208,7 +38337,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38216,34 +38345,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11575</v>
+        <v>11574</v>
       </c>
       <c r="D4" t="n">
-        <v>7644</v>
+        <v>7548</v>
       </c>
       <c r="E4" t="n">
-        <v>1519</v>
+        <v>1589</v>
       </c>
       <c r="F4" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="G4" t="n">
-        <v>1810</v>
+        <v>1832</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>66.04000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="J4" t="n">
-        <v>13.12</v>
+        <v>13.73</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
       <c r="L4" t="n">
-        <v>15.64</v>
+        <v>15.83</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M877"/>
+  <dimension ref="A1:M880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38165,6 +38165,135 @@
         <v>15.83</v>
       </c>
       <c r="M877" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D878" t="n">
+        <v>1701</v>
+      </c>
+      <c r="E878" t="n">
+        <v>1402</v>
+      </c>
+      <c r="F878" t="n">
+        <v>316</v>
+      </c>
+      <c r="G878" t="n">
+        <v>1456</v>
+      </c>
+      <c r="H878" t="n">
+        <v>685</v>
+      </c>
+      <c r="I878" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="J878" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="K878" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L878" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="M878" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>6055</v>
+      </c>
+      <c r="D879" t="n">
+        <v>4039</v>
+      </c>
+      <c r="E879" t="n">
+        <v>1091</v>
+      </c>
+      <c r="F879" t="n">
+        <v>247</v>
+      </c>
+      <c r="G879" t="n">
+        <v>644</v>
+      </c>
+      <c r="H879" t="n">
+        <v>34</v>
+      </c>
+      <c r="I879" t="n">
+        <v>66.70999999999999</v>
+      </c>
+      <c r="J879" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="K879" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L879" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="M879" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>11574</v>
+      </c>
+      <c r="D880" t="n">
+        <v>6997</v>
+      </c>
+      <c r="E880" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F880" t="n">
+        <v>590</v>
+      </c>
+      <c r="G880" t="n">
+        <v>1857</v>
+      </c>
+      <c r="H880" t="n">
+        <v>0</v>
+      </c>
+      <c r="I880" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="J880" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K880" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L880" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="M880" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38251,7 +38380,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38262,31 +38391,31 @@
         <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>2366</v>
+        <v>1701</v>
       </c>
       <c r="E2" t="n">
-        <v>743</v>
+        <v>1402</v>
       </c>
       <c r="F2" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G2" t="n">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="H2" t="n">
         <v>685</v>
       </c>
       <c r="I2" t="n">
-        <v>42.55</v>
+        <v>30.59</v>
       </c>
       <c r="J2" t="n">
-        <v>13.36</v>
+        <v>25.22</v>
       </c>
       <c r="K2" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="L2" t="n">
-        <v>26.04</v>
+        <v>26.19</v>
       </c>
       <c r="M2" t="n">
         <v>12.32</v>
@@ -38294,7 +38423,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38305,31 +38434,31 @@
         <v>6055</v>
       </c>
       <c r="D3" t="n">
-        <v>4203</v>
+        <v>4039</v>
       </c>
       <c r="E3" t="n">
-        <v>930</v>
+        <v>1091</v>
       </c>
       <c r="F3" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G3" t="n">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>69.41</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>15.36</v>
+        <v>18.02</v>
       </c>
       <c r="K3" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="L3" t="n">
-        <v>10.34</v>
+        <v>10.64</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38337,7 +38466,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38348,31 +38477,31 @@
         <v>11574</v>
       </c>
       <c r="D4" t="n">
-        <v>7548</v>
+        <v>6997</v>
       </c>
       <c r="E4" t="n">
-        <v>1589</v>
+        <v>2130</v>
       </c>
       <c r="F4" t="n">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="G4" t="n">
-        <v>1832</v>
+        <v>1857</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>65.22</v>
+        <v>60.45</v>
       </c>
       <c r="J4" t="n">
-        <v>13.73</v>
+        <v>18.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.23</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>15.83</v>
+        <v>16.04</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M880"/>
+  <dimension ref="A1:M883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38294,6 +38294,135 @@
         <v>16.04</v>
       </c>
       <c r="M880" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>5560</v>
+      </c>
+      <c r="D881" t="n">
+        <v>2373</v>
+      </c>
+      <c r="E881" t="n">
+        <v>735</v>
+      </c>
+      <c r="F881" t="n">
+        <v>296</v>
+      </c>
+      <c r="G881" t="n">
+        <v>1472</v>
+      </c>
+      <c r="H881" t="n">
+        <v>684</v>
+      </c>
+      <c r="I881" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="J881" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="K881" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="L881" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="M881" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>6054</v>
+      </c>
+      <c r="D882" t="n">
+        <v>4375</v>
+      </c>
+      <c r="E882" t="n">
+        <v>769</v>
+      </c>
+      <c r="F882" t="n">
+        <v>224</v>
+      </c>
+      <c r="G882" t="n">
+        <v>652</v>
+      </c>
+      <c r="H882" t="n">
+        <v>34</v>
+      </c>
+      <c r="I882" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="J882" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K882" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L882" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="M882" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>11573</v>
+      </c>
+      <c r="D883" t="n">
+        <v>7695</v>
+      </c>
+      <c r="E883" t="n">
+        <v>1444</v>
+      </c>
+      <c r="F883" t="n">
+        <v>551</v>
+      </c>
+      <c r="G883" t="n">
+        <v>1883</v>
+      </c>
+      <c r="H883" t="n">
+        <v>0</v>
+      </c>
+      <c r="I883" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="J883" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="K883" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L883" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="M883" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38380,7 +38509,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38391,39 +38520,39 @@
         <v>5560</v>
       </c>
       <c r="D2" t="n">
-        <v>1701</v>
+        <v>2373</v>
       </c>
       <c r="E2" t="n">
-        <v>1402</v>
+        <v>735</v>
       </c>
       <c r="F2" t="n">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="G2" t="n">
-        <v>1456</v>
+        <v>1472</v>
       </c>
       <c r="H2" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="I2" t="n">
-        <v>30.59</v>
+        <v>42.68</v>
       </c>
       <c r="J2" t="n">
-        <v>25.22</v>
+        <v>13.22</v>
       </c>
       <c r="K2" t="n">
-        <v>5.68</v>
+        <v>5.32</v>
       </c>
       <c r="L2" t="n">
-        <v>26.19</v>
+        <v>26.47</v>
       </c>
       <c r="M2" t="n">
-        <v>12.32</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38431,34 +38560,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6055</v>
+        <v>6054</v>
       </c>
       <c r="D3" t="n">
-        <v>4039</v>
+        <v>4375</v>
       </c>
       <c r="E3" t="n">
-        <v>1091</v>
+        <v>769</v>
       </c>
       <c r="F3" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="G3" t="n">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>66.70999999999999</v>
+        <v>72.27</v>
       </c>
       <c r="J3" t="n">
-        <v>18.02</v>
+        <v>12.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.08</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>10.64</v>
+        <v>10.77</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38466,7 +38595,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38474,34 +38603,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11574</v>
+        <v>11573</v>
       </c>
       <c r="D4" t="n">
-        <v>6997</v>
+        <v>7695</v>
       </c>
       <c r="E4" t="n">
-        <v>2130</v>
+        <v>1444</v>
       </c>
       <c r="F4" t="n">
-        <v>590</v>
+        <v>551</v>
       </c>
       <c r="G4" t="n">
-        <v>1857</v>
+        <v>1883</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>60.45</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>18.4</v>
+        <v>12.48</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>4.76</v>
       </c>
       <c r="L4" t="n">
-        <v>16.04</v>
+        <v>16.27</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M883"/>
+  <dimension ref="A1:M886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38423,6 +38423,135 @@
         <v>16.27</v>
       </c>
       <c r="M883" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>5558</v>
+      </c>
+      <c r="D884" t="n">
+        <v>2582</v>
+      </c>
+      <c r="E884" t="n">
+        <v>525</v>
+      </c>
+      <c r="F884" t="n">
+        <v>298</v>
+      </c>
+      <c r="G884" t="n">
+        <v>1470</v>
+      </c>
+      <c r="H884" t="n">
+        <v>683</v>
+      </c>
+      <c r="I884" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="J884" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="K884" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L884" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="M884" t="n">
+        <v>12.29</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>6050</v>
+      </c>
+      <c r="D885" t="n">
+        <v>4386</v>
+      </c>
+      <c r="E885" t="n">
+        <v>742</v>
+      </c>
+      <c r="F885" t="n">
+        <v>237</v>
+      </c>
+      <c r="G885" t="n">
+        <v>651</v>
+      </c>
+      <c r="H885" t="n">
+        <v>34</v>
+      </c>
+      <c r="I885" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J885" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="K885" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L885" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="M885" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>11567</v>
+      </c>
+      <c r="D886" t="n">
+        <v>7857</v>
+      </c>
+      <c r="E886" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F886" t="n">
+        <v>570</v>
+      </c>
+      <c r="G886" t="n">
+        <v>1891</v>
+      </c>
+      <c r="H886" t="n">
+        <v>0</v>
+      </c>
+      <c r="I886" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="J886" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K886" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L886" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="M886" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38509,7 +38638,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38517,42 +38646,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5560</v>
+        <v>5558</v>
       </c>
       <c r="D2" t="n">
-        <v>2373</v>
+        <v>2582</v>
       </c>
       <c r="E2" t="n">
-        <v>735</v>
+        <v>525</v>
       </c>
       <c r="F2" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G2" t="n">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="H2" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I2" t="n">
-        <v>42.68</v>
+        <v>46.46</v>
       </c>
       <c r="J2" t="n">
-        <v>13.22</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>5.32</v>
+        <v>5.36</v>
       </c>
       <c r="L2" t="n">
-        <v>26.47</v>
+        <v>26.45</v>
       </c>
       <c r="M2" t="n">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38560,34 +38689,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6054</v>
+        <v>6050</v>
       </c>
       <c r="D3" t="n">
-        <v>4375</v>
+        <v>4386</v>
       </c>
       <c r="E3" t="n">
-        <v>769</v>
+        <v>742</v>
       </c>
       <c r="F3" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G3" t="n">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>72.27</v>
+        <v>72.5</v>
       </c>
       <c r="J3" t="n">
-        <v>12.7</v>
+        <v>12.26</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="L3" t="n">
-        <v>10.77</v>
+        <v>10.76</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38595,7 +38724,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38603,34 +38732,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11573</v>
+        <v>11567</v>
       </c>
       <c r="D4" t="n">
-        <v>7695</v>
+        <v>7857</v>
       </c>
       <c r="E4" t="n">
-        <v>1444</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="n">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="G4" t="n">
-        <v>1883</v>
+        <v>1891</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>66.48999999999999</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>12.48</v>
+        <v>10.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.76</v>
+        <v>4.93</v>
       </c>
       <c r="L4" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M886"/>
+  <dimension ref="A1:M889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38552,6 +38552,135 @@
         <v>16.35</v>
       </c>
       <c r="M886" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>5558</v>
+      </c>
+      <c r="D887" t="n">
+        <v>2699</v>
+      </c>
+      <c r="E887" t="n">
+        <v>410</v>
+      </c>
+      <c r="F887" t="n">
+        <v>308</v>
+      </c>
+      <c r="G887" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H887" t="n">
+        <v>681</v>
+      </c>
+      <c r="I887" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="J887" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="K887" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L887" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="M887" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>6050</v>
+      </c>
+      <c r="D888" t="n">
+        <v>4365</v>
+      </c>
+      <c r="E888" t="n">
+        <v>763</v>
+      </c>
+      <c r="F888" t="n">
+        <v>240</v>
+      </c>
+      <c r="G888" t="n">
+        <v>648</v>
+      </c>
+      <c r="H888" t="n">
+        <v>34</v>
+      </c>
+      <c r="I888" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="J888" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="K888" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="L888" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="M888" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>11567</v>
+      </c>
+      <c r="D889" t="n">
+        <v>7946</v>
+      </c>
+      <c r="E889" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F889" t="n">
+        <v>581</v>
+      </c>
+      <c r="G889" t="n">
+        <v>1880</v>
+      </c>
+      <c r="H889" t="n">
+        <v>0</v>
+      </c>
+      <c r="I889" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="J889" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="K889" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="L889" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="M889" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38638,7 +38767,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38649,39 +38778,39 @@
         <v>5558</v>
       </c>
       <c r="D2" t="n">
-        <v>2582</v>
+        <v>2699</v>
       </c>
       <c r="E2" t="n">
-        <v>525</v>
+        <v>410</v>
       </c>
       <c r="F2" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G2" t="n">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="H2" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="I2" t="n">
-        <v>46.46</v>
+        <v>48.56</v>
       </c>
       <c r="J2" t="n">
-        <v>9.449999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="K2" t="n">
-        <v>5.36</v>
+        <v>5.54</v>
       </c>
       <c r="L2" t="n">
-        <v>26.45</v>
+        <v>26.27</v>
       </c>
       <c r="M2" t="n">
-        <v>12.29</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38692,31 +38821,31 @@
         <v>6050</v>
       </c>
       <c r="D3" t="n">
-        <v>4386</v>
+        <v>4365</v>
       </c>
       <c r="E3" t="n">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="F3" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G3" t="n">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>72.5</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>12.26</v>
+        <v>12.61</v>
       </c>
       <c r="K3" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="L3" t="n">
-        <v>10.76</v>
+        <v>10.71</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38724,7 +38853,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38735,31 +38864,31 @@
         <v>11567</v>
       </c>
       <c r="D4" t="n">
-        <v>7857</v>
+        <v>7946</v>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>1160</v>
       </c>
       <c r="F4" t="n">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="G4" t="n">
-        <v>1891</v>
+        <v>1880</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>67.93000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="J4" t="n">
-        <v>10.8</v>
+        <v>10.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.93</v>
+        <v>5.02</v>
       </c>
       <c r="L4" t="n">
-        <v>16.35</v>
+        <v>16.25</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M889"/>
+  <dimension ref="A1:M892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38681,6 +38681,135 @@
         <v>16.25</v>
       </c>
       <c r="M889" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>5558</v>
+      </c>
+      <c r="D890" t="n">
+        <v>2725</v>
+      </c>
+      <c r="E890" t="n">
+        <v>405</v>
+      </c>
+      <c r="F890" t="n">
+        <v>306</v>
+      </c>
+      <c r="G890" t="n">
+        <v>1441</v>
+      </c>
+      <c r="H890" t="n">
+        <v>681</v>
+      </c>
+      <c r="I890" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="J890" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="K890" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="L890" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="M890" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>6049</v>
+      </c>
+      <c r="D891" t="n">
+        <v>4322</v>
+      </c>
+      <c r="E891" t="n">
+        <v>813</v>
+      </c>
+      <c r="F891" t="n">
+        <v>231</v>
+      </c>
+      <c r="G891" t="n">
+        <v>649</v>
+      </c>
+      <c r="H891" t="n">
+        <v>34</v>
+      </c>
+      <c r="I891" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="J891" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="K891" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="L891" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="M891" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>11566</v>
+      </c>
+      <c r="D892" t="n">
+        <v>7928</v>
+      </c>
+      <c r="E892" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F892" t="n">
+        <v>577</v>
+      </c>
+      <c r="G892" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H892" t="n">
+        <v>0</v>
+      </c>
+      <c r="I892" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="J892" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="K892" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="L892" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="M892" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38767,7 +38896,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38778,31 +38907,31 @@
         <v>5558</v>
       </c>
       <c r="D2" t="n">
-        <v>2699</v>
+        <v>2725</v>
       </c>
       <c r="E2" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F2" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G2" t="n">
-        <v>1460</v>
+        <v>1441</v>
       </c>
       <c r="H2" t="n">
         <v>681</v>
       </c>
       <c r="I2" t="n">
-        <v>48.56</v>
+        <v>49.03</v>
       </c>
       <c r="J2" t="n">
-        <v>7.38</v>
+        <v>7.29</v>
       </c>
       <c r="K2" t="n">
-        <v>5.54</v>
+        <v>5.51</v>
       </c>
       <c r="L2" t="n">
-        <v>26.27</v>
+        <v>25.93</v>
       </c>
       <c r="M2" t="n">
         <v>12.25</v>
@@ -38810,7 +38939,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38818,34 +38947,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6050</v>
+        <v>6049</v>
       </c>
       <c r="D3" t="n">
-        <v>4365</v>
+        <v>4322</v>
       </c>
       <c r="E3" t="n">
-        <v>763</v>
+        <v>813</v>
       </c>
       <c r="F3" t="n">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="G3" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>72.15000000000001</v>
+        <v>71.45</v>
       </c>
       <c r="J3" t="n">
-        <v>12.61</v>
+        <v>13.44</v>
       </c>
       <c r="K3" t="n">
-        <v>3.97</v>
+        <v>3.82</v>
       </c>
       <c r="L3" t="n">
-        <v>10.71</v>
+        <v>10.73</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38853,7 +38982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38861,34 +38990,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11567</v>
+        <v>11566</v>
       </c>
       <c r="D4" t="n">
-        <v>7946</v>
+        <v>7928</v>
       </c>
       <c r="E4" t="n">
-        <v>1160</v>
+        <v>1189</v>
       </c>
       <c r="F4" t="n">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G4" t="n">
-        <v>1880</v>
+        <v>1872</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.7</v>
+        <v>68.55</v>
       </c>
       <c r="J4" t="n">
-        <v>10.03</v>
+        <v>10.28</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02</v>
+        <v>4.99</v>
       </c>
       <c r="L4" t="n">
-        <v>16.25</v>
+        <v>16.19</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M892"/>
+  <dimension ref="A1:M895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38810,6 +38810,135 @@
         <v>16.19</v>
       </c>
       <c r="M892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D893" t="n">
+        <v>2695</v>
+      </c>
+      <c r="E893" t="n">
+        <v>425</v>
+      </c>
+      <c r="F893" t="n">
+        <v>310</v>
+      </c>
+      <c r="G893" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H893" t="n">
+        <v>679</v>
+      </c>
+      <c r="I893" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J893" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="K893" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L893" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="M893" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>6046</v>
+      </c>
+      <c r="D894" t="n">
+        <v>4327</v>
+      </c>
+      <c r="E894" t="n">
+        <v>805</v>
+      </c>
+      <c r="F894" t="n">
+        <v>235</v>
+      </c>
+      <c r="G894" t="n">
+        <v>645</v>
+      </c>
+      <c r="H894" t="n">
+        <v>34</v>
+      </c>
+      <c r="I894" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="J894" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="K894" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L894" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="M894" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>11562</v>
+      </c>
+      <c r="D895" t="n">
+        <v>7908</v>
+      </c>
+      <c r="E895" t="n">
+        <v>1216</v>
+      </c>
+      <c r="F895" t="n">
+        <v>568</v>
+      </c>
+      <c r="G895" t="n">
+        <v>1870</v>
+      </c>
+      <c r="H895" t="n">
+        <v>0</v>
+      </c>
+      <c r="I895" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J895" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="K895" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L895" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="M895" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38896,7 +39025,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -38904,42 +39033,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="D2" t="n">
-        <v>2725</v>
+        <v>2695</v>
       </c>
       <c r="E2" t="n">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="F2" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G2" t="n">
-        <v>1441</v>
+        <v>1448</v>
       </c>
       <c r="H2" t="n">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="I2" t="n">
-        <v>49.03</v>
+        <v>48.5</v>
       </c>
       <c r="J2" t="n">
-        <v>7.29</v>
+        <v>7.65</v>
       </c>
       <c r="K2" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="L2" t="n">
-        <v>25.93</v>
+        <v>26.06</v>
       </c>
       <c r="M2" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -38947,34 +39076,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6049</v>
+        <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>4322</v>
+        <v>4327</v>
       </c>
       <c r="E3" t="n">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="F3" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G3" t="n">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>71.45</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>13.44</v>
+        <v>13.31</v>
       </c>
       <c r="K3" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="L3" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -38982,7 +39111,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -38990,34 +39119,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11566</v>
+        <v>11562</v>
       </c>
       <c r="D4" t="n">
-        <v>7928</v>
+        <v>7908</v>
       </c>
       <c r="E4" t="n">
-        <v>1189</v>
+        <v>1216</v>
       </c>
       <c r="F4" t="n">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="G4" t="n">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.55</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>10.28</v>
+        <v>10.52</v>
       </c>
       <c r="K4" t="n">
-        <v>4.99</v>
+        <v>4.91</v>
       </c>
       <c r="L4" t="n">
-        <v>16.19</v>
+        <v>16.17</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M895"/>
+  <dimension ref="A1:M898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38939,6 +38939,135 @@
         <v>16.17</v>
       </c>
       <c r="M895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D896" t="n">
+        <v>2661</v>
+      </c>
+      <c r="E896" t="n">
+        <v>455</v>
+      </c>
+      <c r="F896" t="n">
+        <v>304</v>
+      </c>
+      <c r="G896" t="n">
+        <v>1458</v>
+      </c>
+      <c r="H896" t="n">
+        <v>679</v>
+      </c>
+      <c r="I896" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="J896" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="K896" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L896" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="M896" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>6046</v>
+      </c>
+      <c r="D897" t="n">
+        <v>4590</v>
+      </c>
+      <c r="E897" t="n">
+        <v>554</v>
+      </c>
+      <c r="F897" t="n">
+        <v>233</v>
+      </c>
+      <c r="G897" t="n">
+        <v>635</v>
+      </c>
+      <c r="H897" t="n">
+        <v>34</v>
+      </c>
+      <c r="I897" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="J897" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K897" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L897" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M897" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>11562</v>
+      </c>
+      <c r="D898" t="n">
+        <v>8139</v>
+      </c>
+      <c r="E898" t="n">
+        <v>993</v>
+      </c>
+      <c r="F898" t="n">
+        <v>558</v>
+      </c>
+      <c r="G898" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H898" t="n">
+        <v>0</v>
+      </c>
+      <c r="I898" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="J898" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="K898" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="L898" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="M898" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39025,7 +39154,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39036,31 +39165,31 @@
         <v>5557</v>
       </c>
       <c r="D2" t="n">
-        <v>2695</v>
+        <v>2661</v>
       </c>
       <c r="E2" t="n">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="F2" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G2" t="n">
-        <v>1448</v>
+        <v>1458</v>
       </c>
       <c r="H2" t="n">
         <v>679</v>
       </c>
       <c r="I2" t="n">
-        <v>48.5</v>
+        <v>47.89</v>
       </c>
       <c r="J2" t="n">
-        <v>7.65</v>
+        <v>8.19</v>
       </c>
       <c r="K2" t="n">
-        <v>5.58</v>
+        <v>5.47</v>
       </c>
       <c r="L2" t="n">
-        <v>26.06</v>
+        <v>26.24</v>
       </c>
       <c r="M2" t="n">
         <v>12.22</v>
@@ -39068,7 +39197,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39079,31 +39208,31 @@
         <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>4327</v>
+        <v>4590</v>
       </c>
       <c r="E3" t="n">
-        <v>805</v>
+        <v>554</v>
       </c>
       <c r="F3" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G3" t="n">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>71.56999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="J3" t="n">
-        <v>13.31</v>
+        <v>9.16</v>
       </c>
       <c r="K3" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -39111,7 +39240,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39122,31 +39251,31 @@
         <v>11562</v>
       </c>
       <c r="D4" t="n">
-        <v>7908</v>
+        <v>8139</v>
       </c>
       <c r="E4" t="n">
-        <v>1216</v>
+        <v>993</v>
       </c>
       <c r="F4" t="n">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="G4" t="n">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.40000000000001</v>
+        <v>70.39</v>
       </c>
       <c r="J4" t="n">
-        <v>10.52</v>
+        <v>8.59</v>
       </c>
       <c r="K4" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="L4" t="n">
-        <v>16.17</v>
+        <v>16.19</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M898"/>
+  <dimension ref="A1:M901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39068,6 +39068,135 @@
         <v>16.19</v>
       </c>
       <c r="M898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D899" t="n">
+        <v>2558</v>
+      </c>
+      <c r="E899" t="n">
+        <v>552</v>
+      </c>
+      <c r="F899" t="n">
+        <v>297</v>
+      </c>
+      <c r="G899" t="n">
+        <v>1472</v>
+      </c>
+      <c r="H899" t="n">
+        <v>678</v>
+      </c>
+      <c r="I899" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="J899" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="K899" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="L899" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="M899" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>6046</v>
+      </c>
+      <c r="D900" t="n">
+        <v>4604</v>
+      </c>
+      <c r="E900" t="n">
+        <v>539</v>
+      </c>
+      <c r="F900" t="n">
+        <v>233</v>
+      </c>
+      <c r="G900" t="n">
+        <v>636</v>
+      </c>
+      <c r="H900" t="n">
+        <v>34</v>
+      </c>
+      <c r="I900" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="J900" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="K900" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L900" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="M900" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>11562</v>
+      </c>
+      <c r="D901" t="n">
+        <v>8055</v>
+      </c>
+      <c r="E901" t="n">
+        <v>1074</v>
+      </c>
+      <c r="F901" t="n">
+        <v>538</v>
+      </c>
+      <c r="G901" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H901" t="n">
+        <v>0</v>
+      </c>
+      <c r="I901" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="J901" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K901" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L901" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="M901" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39154,7 +39283,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39165,39 +39294,39 @@
         <v>5557</v>
       </c>
       <c r="D2" t="n">
-        <v>2661</v>
+        <v>2558</v>
       </c>
       <c r="E2" t="n">
-        <v>455</v>
+        <v>552</v>
       </c>
       <c r="F2" t="n">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G2" t="n">
-        <v>1458</v>
+        <v>1472</v>
       </c>
       <c r="H2" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I2" t="n">
-        <v>47.89</v>
+        <v>46.03</v>
       </c>
       <c r="J2" t="n">
-        <v>8.19</v>
+        <v>9.93</v>
       </c>
       <c r="K2" t="n">
-        <v>5.47</v>
+        <v>5.34</v>
       </c>
       <c r="L2" t="n">
-        <v>26.24</v>
+        <v>26.49</v>
       </c>
       <c r="M2" t="n">
-        <v>12.22</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39208,31 +39337,31 @@
         <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>4590</v>
+        <v>4604</v>
       </c>
       <c r="E3" t="n">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="F3" t="n">
         <v>233</v>
       </c>
       <c r="G3" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>75.92</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>9.16</v>
+        <v>8.91</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>10.5</v>
+        <v>10.52</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -39240,7 +39369,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39251,31 +39380,31 @@
         <v>11562</v>
       </c>
       <c r="D4" t="n">
-        <v>8139</v>
+        <v>8055</v>
       </c>
       <c r="E4" t="n">
-        <v>993</v>
+        <v>1074</v>
       </c>
       <c r="F4" t="n">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="G4" t="n">
-        <v>1872</v>
+        <v>1895</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.39</v>
+        <v>69.67</v>
       </c>
       <c r="J4" t="n">
-        <v>8.59</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>4.83</v>
+        <v>4.65</v>
       </c>
       <c r="L4" t="n">
-        <v>16.19</v>
+        <v>16.39</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M901"/>
+  <dimension ref="A1:M904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39197,6 +39197,135 @@
         <v>16.39</v>
       </c>
       <c r="M901" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>5558</v>
+      </c>
+      <c r="D902" t="n">
+        <v>2531</v>
+      </c>
+      <c r="E902" t="n">
+        <v>584</v>
+      </c>
+      <c r="F902" t="n">
+        <v>275</v>
+      </c>
+      <c r="G902" t="n">
+        <v>1489</v>
+      </c>
+      <c r="H902" t="n">
+        <v>679</v>
+      </c>
+      <c r="I902" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="J902" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="K902" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="L902" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="M902" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>6046</v>
+      </c>
+      <c r="D903" t="n">
+        <v>4546</v>
+      </c>
+      <c r="E903" t="n">
+        <v>601</v>
+      </c>
+      <c r="F903" t="n">
+        <v>227</v>
+      </c>
+      <c r="G903" t="n">
+        <v>638</v>
+      </c>
+      <c r="H903" t="n">
+        <v>34</v>
+      </c>
+      <c r="I903" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="J903" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="K903" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L903" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="M903" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>11563</v>
+      </c>
+      <c r="D904" t="n">
+        <v>7986</v>
+      </c>
+      <c r="E904" t="n">
+        <v>1151</v>
+      </c>
+      <c r="F904" t="n">
+        <v>499</v>
+      </c>
+      <c r="G904" t="n">
+        <v>1927</v>
+      </c>
+      <c r="H904" t="n">
+        <v>0</v>
+      </c>
+      <c r="I904" t="n">
+        <v>69.06999999999999</v>
+      </c>
+      <c r="J904" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="K904" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L904" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="M904" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39283,7 +39412,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39291,42 +39420,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5557</v>
+        <v>5558</v>
       </c>
       <c r="D2" t="n">
-        <v>2558</v>
+        <v>2531</v>
       </c>
       <c r="E2" t="n">
-        <v>552</v>
+        <v>584</v>
       </c>
       <c r="F2" t="n">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="G2" t="n">
-        <v>1472</v>
+        <v>1489</v>
       </c>
       <c r="H2" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I2" t="n">
-        <v>46.03</v>
+        <v>45.54</v>
       </c>
       <c r="J2" t="n">
-        <v>9.93</v>
+        <v>10.51</v>
       </c>
       <c r="K2" t="n">
-        <v>5.34</v>
+        <v>4.95</v>
       </c>
       <c r="L2" t="n">
-        <v>26.49</v>
+        <v>26.79</v>
       </c>
       <c r="M2" t="n">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39337,31 +39466,31 @@
         <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>4604</v>
+        <v>4546</v>
       </c>
       <c r="E3" t="n">
-        <v>539</v>
+        <v>601</v>
       </c>
       <c r="F3" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G3" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>76.15000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="J3" t="n">
-        <v>8.91</v>
+        <v>9.94</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>10.52</v>
+        <v>10.55</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -39369,7 +39498,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39377,34 +39506,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11562</v>
+        <v>11563</v>
       </c>
       <c r="D4" t="n">
-        <v>8055</v>
+        <v>7986</v>
       </c>
       <c r="E4" t="n">
-        <v>1074</v>
+        <v>1151</v>
       </c>
       <c r="F4" t="n">
-        <v>538</v>
+        <v>499</v>
       </c>
       <c r="G4" t="n">
-        <v>1895</v>
+        <v>1927</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.67</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>4.65</v>
+        <v>4.32</v>
       </c>
       <c r="L4" t="n">
-        <v>16.39</v>
+        <v>16.67</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M904"/>
+  <dimension ref="A1:M907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39326,6 +39326,135 @@
         <v>16.67</v>
       </c>
       <c r="M904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D905" t="n">
+        <v>2611</v>
+      </c>
+      <c r="E905" t="n">
+        <v>502</v>
+      </c>
+      <c r="F905" t="n">
+        <v>265</v>
+      </c>
+      <c r="G905" t="n">
+        <v>1504</v>
+      </c>
+      <c r="H905" t="n">
+        <v>675</v>
+      </c>
+      <c r="I905" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="J905" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="K905" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="L905" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="M905" t="n">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>6047</v>
+      </c>
+      <c r="D906" t="n">
+        <v>4596</v>
+      </c>
+      <c r="E906" t="n">
+        <v>540</v>
+      </c>
+      <c r="F906" t="n">
+        <v>232</v>
+      </c>
+      <c r="G906" t="n">
+        <v>645</v>
+      </c>
+      <c r="H906" t="n">
+        <v>34</v>
+      </c>
+      <c r="I906" t="n">
+        <v>76</v>
+      </c>
+      <c r="J906" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K906" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="L906" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="M906" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>11563</v>
+      </c>
+      <c r="D907" t="n">
+        <v>8099</v>
+      </c>
+      <c r="E907" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F907" t="n">
+        <v>509</v>
+      </c>
+      <c r="G907" t="n">
+        <v>1937</v>
+      </c>
+      <c r="H907" t="n">
+        <v>0</v>
+      </c>
+      <c r="I907" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="J907" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K907" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L907" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="M907" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39412,7 +39541,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39420,42 +39549,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="D2" t="n">
-        <v>2531</v>
+        <v>2611</v>
       </c>
       <c r="E2" t="n">
-        <v>584</v>
+        <v>502</v>
       </c>
       <c r="F2" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G2" t="n">
-        <v>1489</v>
+        <v>1504</v>
       </c>
       <c r="H2" t="n">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="I2" t="n">
-        <v>45.54</v>
+        <v>46.99</v>
       </c>
       <c r="J2" t="n">
-        <v>10.51</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>4.95</v>
+        <v>4.77</v>
       </c>
       <c r="L2" t="n">
-        <v>26.79</v>
+        <v>27.06</v>
       </c>
       <c r="M2" t="n">
-        <v>12.22</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39463,34 +39592,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="D3" t="n">
-        <v>4546</v>
+        <v>4596</v>
       </c>
       <c r="E3" t="n">
-        <v>601</v>
+        <v>540</v>
       </c>
       <c r="F3" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G3" t="n">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>75.19</v>
+        <v>76</v>
       </c>
       <c r="J3" t="n">
-        <v>9.94</v>
+        <v>8.93</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="L3" t="n">
-        <v>10.55</v>
+        <v>10.67</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -39498,7 +39627,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39509,31 +39638,31 @@
         <v>11563</v>
       </c>
       <c r="D4" t="n">
-        <v>7986</v>
+        <v>8099</v>
       </c>
       <c r="E4" t="n">
-        <v>1151</v>
+        <v>1018</v>
       </c>
       <c r="F4" t="n">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="G4" t="n">
-        <v>1927</v>
+        <v>1937</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.06999999999999</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>9.949999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>16.67</v>
+        <v>16.75</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M907"/>
+  <dimension ref="A1:M910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39455,6 +39455,135 @@
         <v>16.75</v>
       </c>
       <c r="M907" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D908" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E908" t="n">
+        <v>421</v>
+      </c>
+      <c r="F908" t="n">
+        <v>254</v>
+      </c>
+      <c r="G908" t="n">
+        <v>1508</v>
+      </c>
+      <c r="H908" t="n">
+        <v>674</v>
+      </c>
+      <c r="I908" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="J908" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="K908" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L908" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="M908" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>6046</v>
+      </c>
+      <c r="D909" t="n">
+        <v>4637</v>
+      </c>
+      <c r="E909" t="n">
+        <v>490</v>
+      </c>
+      <c r="F909" t="n">
+        <v>214</v>
+      </c>
+      <c r="G909" t="n">
+        <v>671</v>
+      </c>
+      <c r="H909" t="n">
+        <v>34</v>
+      </c>
+      <c r="I909" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J909" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K909" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L909" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M909" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>11562</v>
+      </c>
+      <c r="D910" t="n">
+        <v>8206</v>
+      </c>
+      <c r="E910" t="n">
+        <v>907</v>
+      </c>
+      <c r="F910" t="n">
+        <v>452</v>
+      </c>
+      <c r="G910" t="n">
+        <v>1997</v>
+      </c>
+      <c r="H910" t="n">
+        <v>0</v>
+      </c>
+      <c r="I910" t="n">
+        <v>70.97</v>
+      </c>
+      <c r="J910" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="K910" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L910" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="M910" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39541,7 +39670,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39552,39 +39681,39 @@
         <v>5557</v>
       </c>
       <c r="D2" t="n">
-        <v>2611</v>
+        <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>502</v>
+        <v>421</v>
       </c>
       <c r="F2" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="G2" t="n">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="H2" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I2" t="n">
-        <v>46.99</v>
+        <v>48.59</v>
       </c>
       <c r="J2" t="n">
-        <v>9.029999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="K2" t="n">
-        <v>4.77</v>
+        <v>4.57</v>
       </c>
       <c r="L2" t="n">
-        <v>27.06</v>
+        <v>27.14</v>
       </c>
       <c r="M2" t="n">
-        <v>12.15</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39592,34 +39721,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6047</v>
+        <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>4596</v>
+        <v>4637</v>
       </c>
       <c r="E3" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="F3" t="n">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="G3" t="n">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>76</v>
+        <v>76.7</v>
       </c>
       <c r="J3" t="n">
-        <v>8.93</v>
+        <v>8.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.84</v>
+        <v>3.54</v>
       </c>
       <c r="L3" t="n">
-        <v>10.67</v>
+        <v>11.1</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -39627,7 +39756,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39635,34 +39764,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11563</v>
+        <v>11562</v>
       </c>
       <c r="D4" t="n">
-        <v>8099</v>
+        <v>8206</v>
       </c>
       <c r="E4" t="n">
-        <v>1018</v>
+        <v>907</v>
       </c>
       <c r="F4" t="n">
-        <v>509</v>
+        <v>452</v>
       </c>
       <c r="G4" t="n">
-        <v>1937</v>
+        <v>1997</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.04000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>3.91</v>
       </c>
       <c r="L4" t="n">
-        <v>16.75</v>
+        <v>17.27</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M910"/>
+  <dimension ref="A1:M913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39584,6 +39584,135 @@
         <v>17.27</v>
       </c>
       <c r="M910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D911" t="n">
+        <v>2735</v>
+      </c>
+      <c r="E911" t="n">
+        <v>394</v>
+      </c>
+      <c r="F911" t="n">
+        <v>243</v>
+      </c>
+      <c r="G911" t="n">
+        <v>1511</v>
+      </c>
+      <c r="H911" t="n">
+        <v>672</v>
+      </c>
+      <c r="I911" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="J911" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="K911" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="L911" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="M911" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>6044</v>
+      </c>
+      <c r="D912" t="n">
+        <v>4636</v>
+      </c>
+      <c r="E912" t="n">
+        <v>495</v>
+      </c>
+      <c r="F912" t="n">
+        <v>218</v>
+      </c>
+      <c r="G912" t="n">
+        <v>661</v>
+      </c>
+      <c r="H912" t="n">
+        <v>34</v>
+      </c>
+      <c r="I912" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J912" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="K912" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="L912" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="M912" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>11558</v>
+      </c>
+      <c r="D913" t="n">
+        <v>8202</v>
+      </c>
+      <c r="E913" t="n">
+        <v>912</v>
+      </c>
+      <c r="F913" t="n">
+        <v>459</v>
+      </c>
+      <c r="G913" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H913" t="n">
+        <v>0</v>
+      </c>
+      <c r="I913" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="J913" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="K913" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="L913" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="M913" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39670,7 +39799,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39678,42 +39807,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5557</v>
+        <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2700</v>
+        <v>2735</v>
       </c>
       <c r="E2" t="n">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="F2" t="n">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G2" t="n">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="H2" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="I2" t="n">
-        <v>48.59</v>
+        <v>49.23</v>
       </c>
       <c r="J2" t="n">
-        <v>7.58</v>
+        <v>7.09</v>
       </c>
       <c r="K2" t="n">
-        <v>4.57</v>
+        <v>4.37</v>
       </c>
       <c r="L2" t="n">
-        <v>27.14</v>
+        <v>27.2</v>
       </c>
       <c r="M2" t="n">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39721,19 +39850,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6046</v>
+        <v>6044</v>
       </c>
       <c r="D3" t="n">
-        <v>4637</v>
+        <v>4636</v>
       </c>
       <c r="E3" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F3" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G3" t="n">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="H3" t="n">
         <v>34</v>
@@ -39742,13 +39871,13 @@
         <v>76.7</v>
       </c>
       <c r="J3" t="n">
-        <v>8.1</v>
+        <v>8.19</v>
       </c>
       <c r="K3" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="L3" t="n">
-        <v>11.1</v>
+        <v>10.94</v>
       </c>
       <c r="M3" t="n">
         <v>0.5600000000000001</v>
@@ -39756,7 +39885,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39764,34 +39893,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11562</v>
+        <v>11558</v>
       </c>
       <c r="D4" t="n">
-        <v>8206</v>
+        <v>8202</v>
       </c>
       <c r="E4" t="n">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="F4" t="n">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="G4" t="n">
-        <v>1997</v>
+        <v>1985</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.97</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>7.84</v>
+        <v>7.89</v>
       </c>
       <c r="K4" t="n">
-        <v>3.91</v>
+        <v>3.97</v>
       </c>
       <c r="L4" t="n">
-        <v>17.27</v>
+        <v>17.17</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M913"/>
+  <dimension ref="A1:M916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39713,6 +39713,135 @@
         <v>17.17</v>
       </c>
       <c r="M913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D914" t="n">
+        <v>2736</v>
+      </c>
+      <c r="E914" t="n">
+        <v>403</v>
+      </c>
+      <c r="F914" t="n">
+        <v>245</v>
+      </c>
+      <c r="G914" t="n">
+        <v>1501</v>
+      </c>
+      <c r="H914" t="n">
+        <v>670</v>
+      </c>
+      <c r="I914" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="J914" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="K914" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="L914" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="M914" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>6046</v>
+      </c>
+      <c r="D915" t="n">
+        <v>4622</v>
+      </c>
+      <c r="E915" t="n">
+        <v>509</v>
+      </c>
+      <c r="F915" t="n">
+        <v>208</v>
+      </c>
+      <c r="G915" t="n">
+        <v>671</v>
+      </c>
+      <c r="H915" t="n">
+        <v>36</v>
+      </c>
+      <c r="I915" t="n">
+        <v>76.45</v>
+      </c>
+      <c r="J915" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="K915" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L915" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M915" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>11558</v>
+      </c>
+      <c r="D916" t="n">
+        <v>8188</v>
+      </c>
+      <c r="E916" t="n">
+        <v>924</v>
+      </c>
+      <c r="F916" t="n">
+        <v>454</v>
+      </c>
+      <c r="G916" t="n">
+        <v>1992</v>
+      </c>
+      <c r="H916" t="n">
+        <v>0</v>
+      </c>
+      <c r="I916" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="J916" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="K916" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="L916" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="M916" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39799,7 +39928,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39810,39 +39939,39 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="E2" t="n">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F2" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G2" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="H2" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="I2" t="n">
-        <v>49.23</v>
+        <v>49.25</v>
       </c>
       <c r="J2" t="n">
-        <v>7.09</v>
+        <v>7.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.37</v>
+        <v>4.41</v>
       </c>
       <c r="L2" t="n">
-        <v>27.2</v>
+        <v>27.02</v>
       </c>
       <c r="M2" t="n">
-        <v>12.1</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39850,42 +39979,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6044</v>
+        <v>6046</v>
       </c>
       <c r="D3" t="n">
-        <v>4636</v>
+        <v>4622</v>
       </c>
       <c r="E3" t="n">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="F3" t="n">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G3" t="n">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="H3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>76.7</v>
+        <v>76.45</v>
       </c>
       <c r="J3" t="n">
-        <v>8.19</v>
+        <v>8.42</v>
       </c>
       <c r="K3" t="n">
-        <v>3.61</v>
+        <v>3.44</v>
       </c>
       <c r="L3" t="n">
-        <v>10.94</v>
+        <v>11.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -39896,31 +40025,31 @@
         <v>11558</v>
       </c>
       <c r="D4" t="n">
-        <v>8202</v>
+        <v>8188</v>
       </c>
       <c r="E4" t="n">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="F4" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G4" t="n">
-        <v>1985</v>
+        <v>1992</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.95999999999999</v>
+        <v>70.84</v>
       </c>
       <c r="J4" t="n">
-        <v>7.89</v>
+        <v>7.99</v>
       </c>
       <c r="K4" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="L4" t="n">
-        <v>17.17</v>
+        <v>17.23</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M916"/>
+  <dimension ref="A1:M919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39842,6 +39842,135 @@
         <v>17.23</v>
       </c>
       <c r="M916" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D917" t="n">
+        <v>2696</v>
+      </c>
+      <c r="E917" t="n">
+        <v>452</v>
+      </c>
+      <c r="F917" t="n">
+        <v>229</v>
+      </c>
+      <c r="G917" t="n">
+        <v>1508</v>
+      </c>
+      <c r="H917" t="n">
+        <v>670</v>
+      </c>
+      <c r="I917" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="J917" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="K917" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L917" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="M917" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>6047</v>
+      </c>
+      <c r="D918" t="n">
+        <v>4619</v>
+      </c>
+      <c r="E918" t="n">
+        <v>519</v>
+      </c>
+      <c r="F918" t="n">
+        <v>198</v>
+      </c>
+      <c r="G918" t="n">
+        <v>675</v>
+      </c>
+      <c r="H918" t="n">
+        <v>36</v>
+      </c>
+      <c r="I918" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="J918" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="K918" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L918" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M918" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>11559</v>
+      </c>
+      <c r="D919" t="n">
+        <v>8136</v>
+      </c>
+      <c r="E919" t="n">
+        <v>991</v>
+      </c>
+      <c r="F919" t="n">
+        <v>431</v>
+      </c>
+      <c r="G919" t="n">
+        <v>2001</v>
+      </c>
+      <c r="H919" t="n">
+        <v>0</v>
+      </c>
+      <c r="I919" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="J919" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="K919" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="L919" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="M919" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39928,7 +40057,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -39939,31 +40068,31 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2736</v>
+        <v>2696</v>
       </c>
       <c r="E2" t="n">
-        <v>403</v>
+        <v>452</v>
       </c>
       <c r="F2" t="n">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="H2" t="n">
         <v>670</v>
       </c>
       <c r="I2" t="n">
-        <v>49.25</v>
+        <v>48.53</v>
       </c>
       <c r="J2" t="n">
-        <v>7.25</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>4.41</v>
+        <v>4.12</v>
       </c>
       <c r="L2" t="n">
-        <v>27.02</v>
+        <v>27.15</v>
       </c>
       <c r="M2" t="n">
         <v>12.06</v>
@@ -39971,7 +40100,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -39979,34 +40108,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="D3" t="n">
-        <v>4622</v>
+        <v>4619</v>
       </c>
       <c r="E3" t="n">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="G3" t="n">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>76.45</v>
+        <v>76.38</v>
       </c>
       <c r="J3" t="n">
-        <v>8.42</v>
+        <v>8.58</v>
       </c>
       <c r="K3" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="L3" t="n">
-        <v>11.1</v>
+        <v>11.16</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -40014,7 +40143,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40022,34 +40151,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11558</v>
+        <v>11559</v>
       </c>
       <c r="D4" t="n">
-        <v>8188</v>
+        <v>8136</v>
       </c>
       <c r="E4" t="n">
-        <v>924</v>
+        <v>991</v>
       </c>
       <c r="F4" t="n">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="G4" t="n">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.84</v>
+        <v>70.39</v>
       </c>
       <c r="J4" t="n">
-        <v>7.99</v>
+        <v>8.57</v>
       </c>
       <c r="K4" t="n">
-        <v>3.93</v>
+        <v>3.73</v>
       </c>
       <c r="L4" t="n">
-        <v>17.23</v>
+        <v>17.31</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M919"/>
+  <dimension ref="A1:M922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39971,6 +39971,135 @@
         <v>17.31</v>
       </c>
       <c r="M919" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D920" t="n">
+        <v>2555</v>
+      </c>
+      <c r="E920" t="n">
+        <v>603</v>
+      </c>
+      <c r="F920" t="n">
+        <v>211</v>
+      </c>
+      <c r="G920" t="n">
+        <v>1516</v>
+      </c>
+      <c r="H920" t="n">
+        <v>670</v>
+      </c>
+      <c r="I920" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="J920" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="K920" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L920" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="M920" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>6047</v>
+      </c>
+      <c r="D921" t="n">
+        <v>4513</v>
+      </c>
+      <c r="E921" t="n">
+        <v>621</v>
+      </c>
+      <c r="F921" t="n">
+        <v>199</v>
+      </c>
+      <c r="G921" t="n">
+        <v>678</v>
+      </c>
+      <c r="H921" t="n">
+        <v>36</v>
+      </c>
+      <c r="I921" t="n">
+        <v>74.63</v>
+      </c>
+      <c r="J921" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="K921" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L921" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="M921" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>11559</v>
+      </c>
+      <c r="D922" t="n">
+        <v>7921</v>
+      </c>
+      <c r="E922" t="n">
+        <v>1208</v>
+      </c>
+      <c r="F922" t="n">
+        <v>407</v>
+      </c>
+      <c r="G922" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="n">
+        <v>68.53</v>
+      </c>
+      <c r="J922" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="K922" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L922" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M922" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40057,7 +40186,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40068,31 +40197,31 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2696</v>
+        <v>2555</v>
       </c>
       <c r="E2" t="n">
-        <v>452</v>
+        <v>603</v>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G2" t="n">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="H2" t="n">
         <v>670</v>
       </c>
       <c r="I2" t="n">
-        <v>48.53</v>
+        <v>45.99</v>
       </c>
       <c r="J2" t="n">
-        <v>8.140000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="K2" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>27.15</v>
+        <v>27.29</v>
       </c>
       <c r="M2" t="n">
         <v>12.06</v>
@@ -40100,7 +40229,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40111,31 +40240,31 @@
         <v>6047</v>
       </c>
       <c r="D3" t="n">
-        <v>4619</v>
+        <v>4513</v>
       </c>
       <c r="E3" t="n">
-        <v>519</v>
+        <v>621</v>
       </c>
       <c r="F3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>76.38</v>
+        <v>74.63</v>
       </c>
       <c r="J3" t="n">
-        <v>8.58</v>
+        <v>10.27</v>
       </c>
       <c r="K3" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="L3" t="n">
-        <v>11.16</v>
+        <v>11.21</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -40143,7 +40272,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40154,31 +40283,31 @@
         <v>11559</v>
       </c>
       <c r="D4" t="n">
-        <v>8136</v>
+        <v>7921</v>
       </c>
       <c r="E4" t="n">
-        <v>991</v>
+        <v>1208</v>
       </c>
       <c r="F4" t="n">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="G4" t="n">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.39</v>
+        <v>68.53</v>
       </c>
       <c r="J4" t="n">
-        <v>8.57</v>
+        <v>10.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.73</v>
+        <v>3.52</v>
       </c>
       <c r="L4" t="n">
-        <v>17.31</v>
+        <v>17.5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M922"/>
+  <dimension ref="A1:M925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40100,6 +40100,135 @@
         <v>17.5</v>
       </c>
       <c r="M922" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D923" t="n">
+        <v>2541</v>
+      </c>
+      <c r="E923" t="n">
+        <v>635</v>
+      </c>
+      <c r="F923" t="n">
+        <v>182</v>
+      </c>
+      <c r="G923" t="n">
+        <v>1528</v>
+      </c>
+      <c r="H923" t="n">
+        <v>669</v>
+      </c>
+      <c r="I923" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="J923" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="K923" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="L923" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M923" t="n">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>6040</v>
+      </c>
+      <c r="D924" t="n">
+        <v>4514</v>
+      </c>
+      <c r="E924" t="n">
+        <v>617</v>
+      </c>
+      <c r="F924" t="n">
+        <v>188</v>
+      </c>
+      <c r="G924" t="n">
+        <v>684</v>
+      </c>
+      <c r="H924" t="n">
+        <v>37</v>
+      </c>
+      <c r="I924" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="J924" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="K924" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L924" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="M924" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>11551</v>
+      </c>
+      <c r="D925" t="n">
+        <v>7946</v>
+      </c>
+      <c r="E925" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F925" t="n">
+        <v>376</v>
+      </c>
+      <c r="G925" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H925" t="n">
+        <v>0</v>
+      </c>
+      <c r="I925" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="J925" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="K925" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="L925" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="M925" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40186,7 +40315,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40197,39 +40326,39 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2555</v>
+        <v>2541</v>
       </c>
       <c r="E2" t="n">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="F2" t="n">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="G2" t="n">
-        <v>1516</v>
+        <v>1528</v>
       </c>
       <c r="H2" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I2" t="n">
-        <v>45.99</v>
+        <v>45.74</v>
       </c>
       <c r="J2" t="n">
-        <v>10.86</v>
+        <v>11.43</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="L2" t="n">
-        <v>27.29</v>
+        <v>27.51</v>
       </c>
       <c r="M2" t="n">
-        <v>12.06</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40237,42 +40366,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6047</v>
+        <v>6040</v>
       </c>
       <c r="D3" t="n">
-        <v>4513</v>
+        <v>4514</v>
       </c>
       <c r="E3" t="n">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F3" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G3" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>74.63</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>10.27</v>
+        <v>10.22</v>
       </c>
       <c r="K3" t="n">
-        <v>3.29</v>
+        <v>3.11</v>
       </c>
       <c r="L3" t="n">
-        <v>11.21</v>
+        <v>11.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40280,34 +40409,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11559</v>
+        <v>11551</v>
       </c>
       <c r="D4" t="n">
-        <v>7921</v>
+        <v>7946</v>
       </c>
       <c r="E4" t="n">
-        <v>1208</v>
+        <v>1199</v>
       </c>
       <c r="F4" t="n">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="G4" t="n">
-        <v>2023</v>
+        <v>2030</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.53</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>10.45</v>
+        <v>10.38</v>
       </c>
       <c r="K4" t="n">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="L4" t="n">
-        <v>17.5</v>
+        <v>17.57</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M925"/>
+  <dimension ref="A1:M928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40229,6 +40229,135 @@
         <v>17.57</v>
       </c>
       <c r="M925" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D926" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E926" t="n">
+        <v>544</v>
+      </c>
+      <c r="F926" t="n">
+        <v>191</v>
+      </c>
+      <c r="G926" t="n">
+        <v>1523</v>
+      </c>
+      <c r="H926" t="n">
+        <v>669</v>
+      </c>
+      <c r="I926" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="J926" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="K926" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L926" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="M926" t="n">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>6041</v>
+      </c>
+      <c r="D927" t="n">
+        <v>4565</v>
+      </c>
+      <c r="E927" t="n">
+        <v>576</v>
+      </c>
+      <c r="F927" t="n">
+        <v>185</v>
+      </c>
+      <c r="G927" t="n">
+        <v>679</v>
+      </c>
+      <c r="H927" t="n">
+        <v>36</v>
+      </c>
+      <c r="I927" t="n">
+        <v>75.56999999999999</v>
+      </c>
+      <c r="J927" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="K927" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="L927" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="M927" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>11553</v>
+      </c>
+      <c r="D928" t="n">
+        <v>8044</v>
+      </c>
+      <c r="E928" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F928" t="n">
+        <v>373</v>
+      </c>
+      <c r="G928" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H928" t="n">
+        <v>0</v>
+      </c>
+      <c r="I928" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="J928" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="K928" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L928" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="M928" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40315,7 +40444,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40326,31 +40455,31 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2541</v>
+        <v>2628</v>
       </c>
       <c r="E2" t="n">
-        <v>635</v>
+        <v>544</v>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G2" t="n">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="H2" t="n">
         <v>669</v>
       </c>
       <c r="I2" t="n">
-        <v>45.74</v>
+        <v>47.31</v>
       </c>
       <c r="J2" t="n">
-        <v>11.43</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="L2" t="n">
-        <v>27.51</v>
+        <v>27.42</v>
       </c>
       <c r="M2" t="n">
         <v>12.04</v>
@@ -40358,7 +40487,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40366,42 +40495,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="D3" t="n">
-        <v>4514</v>
+        <v>4565</v>
       </c>
       <c r="E3" t="n">
-        <v>617</v>
+        <v>576</v>
       </c>
       <c r="F3" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G3" t="n">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>74.73999999999999</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>10.22</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="L3" t="n">
-        <v>11.32</v>
+        <v>11.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40409,34 +40538,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11551</v>
+        <v>11553</v>
       </c>
       <c r="D4" t="n">
-        <v>7946</v>
+        <v>8044</v>
       </c>
       <c r="E4" t="n">
-        <v>1199</v>
+        <v>1111</v>
       </c>
       <c r="F4" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G4" t="n">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.79000000000001</v>
+        <v>69.63</v>
       </c>
       <c r="J4" t="n">
-        <v>10.38</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="L4" t="n">
-        <v>17.57</v>
+        <v>17.53</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M928"/>
+  <dimension ref="A1:M931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40358,6 +40358,135 @@
         <v>17.53</v>
       </c>
       <c r="M928" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D929" t="n">
+        <v>2713</v>
+      </c>
+      <c r="E929" t="n">
+        <v>431</v>
+      </c>
+      <c r="F929" t="n">
+        <v>218</v>
+      </c>
+      <c r="G929" t="n">
+        <v>1524</v>
+      </c>
+      <c r="H929" t="n">
+        <v>669</v>
+      </c>
+      <c r="I929" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="J929" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K929" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L929" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="M929" t="n">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>6041</v>
+      </c>
+      <c r="D930" t="n">
+        <v>4566</v>
+      </c>
+      <c r="E930" t="n">
+        <v>571</v>
+      </c>
+      <c r="F930" t="n">
+        <v>190</v>
+      </c>
+      <c r="G930" t="n">
+        <v>678</v>
+      </c>
+      <c r="H930" t="n">
+        <v>36</v>
+      </c>
+      <c r="I930" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="J930" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="K930" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L930" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="M930" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>11553</v>
+      </c>
+      <c r="D931" t="n">
+        <v>8136</v>
+      </c>
+      <c r="E931" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F931" t="n">
+        <v>392</v>
+      </c>
+      <c r="G931" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H931" t="n">
+        <v>0</v>
+      </c>
+      <c r="I931" t="n">
+        <v>70.42</v>
+      </c>
+      <c r="J931" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="K931" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="L931" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="M931" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40444,7 +40573,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40455,31 +40584,31 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2628</v>
+        <v>2713</v>
       </c>
       <c r="E2" t="n">
-        <v>544</v>
+        <v>431</v>
       </c>
       <c r="F2" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="G2" t="n">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2" t="n">
         <v>669</v>
       </c>
       <c r="I2" t="n">
-        <v>47.31</v>
+        <v>48.84</v>
       </c>
       <c r="J2" t="n">
-        <v>9.789999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="K2" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="L2" t="n">
-        <v>27.42</v>
+        <v>27.43</v>
       </c>
       <c r="M2" t="n">
         <v>12.04</v>
@@ -40487,7 +40616,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40498,31 +40627,31 @@
         <v>6041</v>
       </c>
       <c r="D3" t="n">
-        <v>4565</v>
+        <v>4566</v>
       </c>
       <c r="E3" t="n">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G3" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>75.56999999999999</v>
+        <v>75.58</v>
       </c>
       <c r="J3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>11.24</v>
+        <v>11.22</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -40530,7 +40659,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40541,31 +40670,31 @@
         <v>11553</v>
       </c>
       <c r="D4" t="n">
-        <v>8044</v>
+        <v>8136</v>
       </c>
       <c r="E4" t="n">
-        <v>1111</v>
+        <v>1008</v>
       </c>
       <c r="F4" t="n">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="G4" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.63</v>
+        <v>70.42</v>
       </c>
       <c r="J4" t="n">
-        <v>9.619999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="K4" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="L4" t="n">
-        <v>17.53</v>
+        <v>17.46</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M931"/>
+  <dimension ref="A1:M934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40487,6 +40487,135 @@
         <v>17.46</v>
       </c>
       <c r="M931" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D932" t="n">
+        <v>2704</v>
+      </c>
+      <c r="E932" t="n">
+        <v>443</v>
+      </c>
+      <c r="F932" t="n">
+        <v>222</v>
+      </c>
+      <c r="G932" t="n">
+        <v>1517</v>
+      </c>
+      <c r="H932" t="n">
+        <v>669</v>
+      </c>
+      <c r="I932" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="J932" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="K932" t="n">
+        <v>4</v>
+      </c>
+      <c r="L932" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="M932" t="n">
+        <v>12.04</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>6043</v>
+      </c>
+      <c r="D933" t="n">
+        <v>4496</v>
+      </c>
+      <c r="E933" t="n">
+        <v>648</v>
+      </c>
+      <c r="F933" t="n">
+        <v>186</v>
+      </c>
+      <c r="G933" t="n">
+        <v>677</v>
+      </c>
+      <c r="H933" t="n">
+        <v>36</v>
+      </c>
+      <c r="I933" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="J933" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="K933" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L933" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M933" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>11555</v>
+      </c>
+      <c r="D934" t="n">
+        <v>8063</v>
+      </c>
+      <c r="E934" t="n">
+        <v>1081</v>
+      </c>
+      <c r="F934" t="n">
+        <v>389</v>
+      </c>
+      <c r="G934" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H934" t="n">
+        <v>0</v>
+      </c>
+      <c r="I934" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="J934" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K934" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L934" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M934" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40573,7 +40702,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40584,31 +40713,31 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2713</v>
+        <v>2704</v>
       </c>
       <c r="E2" t="n">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="F2" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
-        <v>1524</v>
+        <v>1517</v>
       </c>
       <c r="H2" t="n">
         <v>669</v>
       </c>
       <c r="I2" t="n">
-        <v>48.84</v>
+        <v>48.68</v>
       </c>
       <c r="J2" t="n">
-        <v>7.76</v>
+        <v>7.97</v>
       </c>
       <c r="K2" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>27.43</v>
+        <v>27.31</v>
       </c>
       <c r="M2" t="n">
         <v>12.04</v>
@@ -40616,7 +40745,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40624,34 +40753,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6041</v>
+        <v>6043</v>
       </c>
       <c r="D3" t="n">
-        <v>4566</v>
+        <v>4496</v>
       </c>
       <c r="E3" t="n">
-        <v>571</v>
+        <v>648</v>
       </c>
       <c r="F3" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>75.58</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>9.449999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="L3" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -40659,7 +40788,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40667,34 +40796,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11553</v>
+        <v>11555</v>
       </c>
       <c r="D4" t="n">
-        <v>8136</v>
+        <v>8063</v>
       </c>
       <c r="E4" t="n">
-        <v>1008</v>
+        <v>1081</v>
       </c>
       <c r="F4" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G4" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.42</v>
+        <v>69.78</v>
       </c>
       <c r="J4" t="n">
-        <v>8.73</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="L4" t="n">
-        <v>17.46</v>
+        <v>17.5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M934"/>
+  <dimension ref="A1:M937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40616,6 +40616,135 @@
         <v>17.5</v>
       </c>
       <c r="M934" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D935" t="n">
+        <v>2728</v>
+      </c>
+      <c r="E935" t="n">
+        <v>416</v>
+      </c>
+      <c r="F935" t="n">
+        <v>221</v>
+      </c>
+      <c r="G935" t="n">
+        <v>1523</v>
+      </c>
+      <c r="H935" t="n">
+        <v>667</v>
+      </c>
+      <c r="I935" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="J935" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="K935" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L935" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="M935" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>6038</v>
+      </c>
+      <c r="D936" t="n">
+        <v>4588</v>
+      </c>
+      <c r="E936" t="n">
+        <v>567</v>
+      </c>
+      <c r="F936" t="n">
+        <v>173</v>
+      </c>
+      <c r="G936" t="n">
+        <v>674</v>
+      </c>
+      <c r="H936" t="n">
+        <v>36</v>
+      </c>
+      <c r="I936" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="J936" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="K936" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L936" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M936" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>11550</v>
+      </c>
+      <c r="D937" t="n">
+        <v>8165</v>
+      </c>
+      <c r="E937" t="n">
+        <v>985</v>
+      </c>
+      <c r="F937" t="n">
+        <v>383</v>
+      </c>
+      <c r="G937" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H937" t="n">
+        <v>0</v>
+      </c>
+      <c r="I937" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="J937" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="K937" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="L937" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="M937" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40702,7 +40831,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40713,39 +40842,39 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2704</v>
+        <v>2728</v>
       </c>
       <c r="E2" t="n">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G2" t="n">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="H2" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="I2" t="n">
-        <v>48.68</v>
+        <v>49.11</v>
       </c>
       <c r="J2" t="n">
-        <v>7.97</v>
+        <v>7.49</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="L2" t="n">
-        <v>27.31</v>
+        <v>27.42</v>
       </c>
       <c r="M2" t="n">
-        <v>12.04</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40753,34 +40882,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6043</v>
+        <v>6038</v>
       </c>
       <c r="D3" t="n">
-        <v>4496</v>
+        <v>4588</v>
       </c>
       <c r="E3" t="n">
-        <v>648</v>
+        <v>567</v>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G3" t="n">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>74.40000000000001</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>10.72</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="L3" t="n">
-        <v>11.2</v>
+        <v>11.16</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -40788,7 +40917,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40796,34 +40925,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11555</v>
+        <v>11550</v>
       </c>
       <c r="D4" t="n">
-        <v>8063</v>
+        <v>8165</v>
       </c>
       <c r="E4" t="n">
-        <v>1081</v>
+        <v>985</v>
       </c>
       <c r="F4" t="n">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G4" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.78</v>
+        <v>70.69</v>
       </c>
       <c r="J4" t="n">
-        <v>9.359999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="L4" t="n">
-        <v>17.5</v>
+        <v>17.46</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M937"/>
+  <dimension ref="A1:M940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40745,6 +40745,135 @@
         <v>17.46</v>
       </c>
       <c r="M937" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D938" t="n">
+        <v>2698</v>
+      </c>
+      <c r="E938" t="n">
+        <v>435</v>
+      </c>
+      <c r="F938" t="n">
+        <v>227</v>
+      </c>
+      <c r="G938" t="n">
+        <v>1528</v>
+      </c>
+      <c r="H938" t="n">
+        <v>667</v>
+      </c>
+      <c r="I938" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="J938" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="K938" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L938" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="M938" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>6037</v>
+      </c>
+      <c r="D939" t="n">
+        <v>4614</v>
+      </c>
+      <c r="E939" t="n">
+        <v>530</v>
+      </c>
+      <c r="F939" t="n">
+        <v>191</v>
+      </c>
+      <c r="G939" t="n">
+        <v>666</v>
+      </c>
+      <c r="H939" t="n">
+        <v>36</v>
+      </c>
+      <c r="I939" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="J939" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="K939" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L939" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="M939" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>11549</v>
+      </c>
+      <c r="D940" t="n">
+        <v>8175</v>
+      </c>
+      <c r="E940" t="n">
+        <v>952</v>
+      </c>
+      <c r="F940" t="n">
+        <v>411</v>
+      </c>
+      <c r="G940" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H940" t="n">
+        <v>0</v>
+      </c>
+      <c r="I940" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="J940" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="K940" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L940" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="M940" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40831,7 +40960,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40842,31 +40971,31 @@
         <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2728</v>
+        <v>2698</v>
       </c>
       <c r="E2" t="n">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="F2" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G2" t="n">
-        <v>1523</v>
+        <v>1528</v>
       </c>
       <c r="H2" t="n">
         <v>667</v>
       </c>
       <c r="I2" t="n">
-        <v>49.11</v>
+        <v>48.57</v>
       </c>
       <c r="J2" t="n">
-        <v>7.49</v>
+        <v>7.83</v>
       </c>
       <c r="K2" t="n">
-        <v>3.98</v>
+        <v>4.09</v>
       </c>
       <c r="L2" t="n">
-        <v>27.42</v>
+        <v>27.51</v>
       </c>
       <c r="M2" t="n">
         <v>12.01</v>
@@ -40874,7 +41003,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -40882,34 +41011,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6038</v>
+        <v>6037</v>
       </c>
       <c r="D3" t="n">
-        <v>4588</v>
+        <v>4614</v>
       </c>
       <c r="E3" t="n">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="F3" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="G3" t="n">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>75.98999999999999</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>9.390000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>2.87</v>
+        <v>3.16</v>
       </c>
       <c r="L3" t="n">
-        <v>11.16</v>
+        <v>11.03</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -40917,7 +41046,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -40925,34 +41054,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11550</v>
+        <v>11549</v>
       </c>
       <c r="D4" t="n">
-        <v>8165</v>
+        <v>8175</v>
       </c>
       <c r="E4" t="n">
-        <v>985</v>
+        <v>952</v>
       </c>
       <c r="F4" t="n">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="G4" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.69</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>8.529999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="K4" t="n">
-        <v>3.32</v>
+        <v>3.56</v>
       </c>
       <c r="L4" t="n">
-        <v>17.46</v>
+        <v>17.41</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M940"/>
+  <dimension ref="A1:M943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40874,6 +40874,135 @@
         <v>17.41</v>
       </c>
       <c r="M940" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D941" t="n">
+        <v>2593</v>
+      </c>
+      <c r="E941" t="n">
+        <v>540</v>
+      </c>
+      <c r="F941" t="n">
+        <v>216</v>
+      </c>
+      <c r="G941" t="n">
+        <v>1538</v>
+      </c>
+      <c r="H941" t="n">
+        <v>667</v>
+      </c>
+      <c r="I941" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="J941" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="K941" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L941" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="M941" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>6034</v>
+      </c>
+      <c r="D942" t="n">
+        <v>4549</v>
+      </c>
+      <c r="E942" t="n">
+        <v>591</v>
+      </c>
+      <c r="F942" t="n">
+        <v>193</v>
+      </c>
+      <c r="G942" t="n">
+        <v>665</v>
+      </c>
+      <c r="H942" t="n">
+        <v>36</v>
+      </c>
+      <c r="I942" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="J942" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="K942" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L942" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="M942" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>11545</v>
+      </c>
+      <c r="D943" t="n">
+        <v>8027</v>
+      </c>
+      <c r="E943" t="n">
+        <v>1092</v>
+      </c>
+      <c r="F943" t="n">
+        <v>409</v>
+      </c>
+      <c r="G943" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H943" t="n">
+        <v>0</v>
+      </c>
+      <c r="I943" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="J943" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="K943" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L943" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="M943" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40960,7 +41089,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -40968,34 +41097,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5555</v>
+        <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2698</v>
+        <v>2593</v>
       </c>
       <c r="E2" t="n">
-        <v>435</v>
+        <v>540</v>
       </c>
       <c r="F2" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="H2" t="n">
         <v>667</v>
       </c>
       <c r="I2" t="n">
-        <v>48.57</v>
+        <v>46.69</v>
       </c>
       <c r="J2" t="n">
-        <v>7.83</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>4.09</v>
+        <v>3.89</v>
       </c>
       <c r="L2" t="n">
-        <v>27.51</v>
+        <v>27.69</v>
       </c>
       <c r="M2" t="n">
         <v>12.01</v>
@@ -41003,7 +41132,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41011,34 +41140,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6037</v>
+        <v>6034</v>
       </c>
       <c r="D3" t="n">
-        <v>4614</v>
+        <v>4549</v>
       </c>
       <c r="E3" t="n">
-        <v>530</v>
+        <v>591</v>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G3" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>76.43000000000001</v>
+        <v>75.39</v>
       </c>
       <c r="J3" t="n">
-        <v>8.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>11.03</v>
+        <v>11.02</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -41046,7 +41175,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41054,34 +41183,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11549</v>
+        <v>11545</v>
       </c>
       <c r="D4" t="n">
-        <v>8175</v>
+        <v>8027</v>
       </c>
       <c r="E4" t="n">
-        <v>952</v>
+        <v>1092</v>
       </c>
       <c r="F4" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G4" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.79000000000001</v>
+        <v>69.53</v>
       </c>
       <c r="J4" t="n">
-        <v>8.24</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="L4" t="n">
-        <v>17.41</v>
+        <v>17.47</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M943"/>
+  <dimension ref="A1:M946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41003,6 +41003,135 @@
         <v>17.47</v>
       </c>
       <c r="M943" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D944" t="n">
+        <v>2207</v>
+      </c>
+      <c r="E944" t="n">
+        <v>929</v>
+      </c>
+      <c r="F944" t="n">
+        <v>203</v>
+      </c>
+      <c r="G944" t="n">
+        <v>1548</v>
+      </c>
+      <c r="H944" t="n">
+        <v>667</v>
+      </c>
+      <c r="I944" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="J944" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="K944" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L944" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="M944" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>6034</v>
+      </c>
+      <c r="D945" t="n">
+        <v>4325</v>
+      </c>
+      <c r="E945" t="n">
+        <v>815</v>
+      </c>
+      <c r="F945" t="n">
+        <v>186</v>
+      </c>
+      <c r="G945" t="n">
+        <v>672</v>
+      </c>
+      <c r="H945" t="n">
+        <v>36</v>
+      </c>
+      <c r="I945" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="J945" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="K945" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L945" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="M945" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>11545</v>
+      </c>
+      <c r="D946" t="n">
+        <v>7588</v>
+      </c>
+      <c r="E946" t="n">
+        <v>1528</v>
+      </c>
+      <c r="F946" t="n">
+        <v>396</v>
+      </c>
+      <c r="G946" t="n">
+        <v>2033</v>
+      </c>
+      <c r="H946" t="n">
+        <v>0</v>
+      </c>
+      <c r="I946" t="n">
+        <v>65.73</v>
+      </c>
+      <c r="J946" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="K946" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L946" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="M946" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41089,7 +41218,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41100,31 +41229,31 @@
         <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2593</v>
+        <v>2207</v>
       </c>
       <c r="E2" t="n">
-        <v>540</v>
+        <v>929</v>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="H2" t="n">
         <v>667</v>
       </c>
       <c r="I2" t="n">
-        <v>46.69</v>
+        <v>39.74</v>
       </c>
       <c r="J2" t="n">
-        <v>9.720000000000001</v>
+        <v>16.73</v>
       </c>
       <c r="K2" t="n">
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
       <c r="L2" t="n">
-        <v>27.69</v>
+        <v>27.87</v>
       </c>
       <c r="M2" t="n">
         <v>12.01</v>
@@ -41132,7 +41261,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41143,31 +41272,31 @@
         <v>6034</v>
       </c>
       <c r="D3" t="n">
-        <v>4549</v>
+        <v>4325</v>
       </c>
       <c r="E3" t="n">
-        <v>591</v>
+        <v>815</v>
       </c>
       <c r="F3" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G3" t="n">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>75.39</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>9.789999999999999</v>
+        <v>13.51</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="L3" t="n">
-        <v>11.02</v>
+        <v>11.14</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -41175,7 +41304,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41186,31 +41315,31 @@
         <v>11545</v>
       </c>
       <c r="D4" t="n">
-        <v>8027</v>
+        <v>7588</v>
       </c>
       <c r="E4" t="n">
-        <v>1092</v>
+        <v>1528</v>
       </c>
       <c r="F4" t="n">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="G4" t="n">
-        <v>2017</v>
+        <v>2033</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.53</v>
+        <v>65.73</v>
       </c>
       <c r="J4" t="n">
-        <v>9.460000000000001</v>
+        <v>13.24</v>
       </c>
       <c r="K4" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="L4" t="n">
-        <v>17.47</v>
+        <v>17.61</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M946"/>
+  <dimension ref="A1:M949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41132,6 +41132,135 @@
         <v>17.61</v>
       </c>
       <c r="M946" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D947" t="n">
+        <v>2514</v>
+      </c>
+      <c r="E947" t="n">
+        <v>619</v>
+      </c>
+      <c r="F947" t="n">
+        <v>202</v>
+      </c>
+      <c r="G947" t="n">
+        <v>1552</v>
+      </c>
+      <c r="H947" t="n">
+        <v>667</v>
+      </c>
+      <c r="I947" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="J947" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="K947" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="L947" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="M947" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>6034</v>
+      </c>
+      <c r="D948" t="n">
+        <v>4497</v>
+      </c>
+      <c r="E948" t="n">
+        <v>644</v>
+      </c>
+      <c r="F948" t="n">
+        <v>190</v>
+      </c>
+      <c r="G948" t="n">
+        <v>667</v>
+      </c>
+      <c r="H948" t="n">
+        <v>36</v>
+      </c>
+      <c r="I948" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="J948" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="K948" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L948" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="M948" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>11545</v>
+      </c>
+      <c r="D949" t="n">
+        <v>7930</v>
+      </c>
+      <c r="E949" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F949" t="n">
+        <v>400</v>
+      </c>
+      <c r="G949" t="n">
+        <v>2029</v>
+      </c>
+      <c r="H949" t="n">
+        <v>0</v>
+      </c>
+      <c r="I949" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="J949" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="K949" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L949" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="M949" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41218,7 +41347,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41229,31 +41358,31 @@
         <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2207</v>
+        <v>2514</v>
       </c>
       <c r="E2" t="n">
-        <v>929</v>
+        <v>619</v>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="H2" t="n">
         <v>667</v>
       </c>
       <c r="I2" t="n">
-        <v>39.74</v>
+        <v>45.26</v>
       </c>
       <c r="J2" t="n">
-        <v>16.73</v>
+        <v>11.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="L2" t="n">
-        <v>27.87</v>
+        <v>27.94</v>
       </c>
       <c r="M2" t="n">
         <v>12.01</v>
@@ -41261,7 +41390,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41272,31 +41401,31 @@
         <v>6034</v>
       </c>
       <c r="D3" t="n">
-        <v>4325</v>
+        <v>4497</v>
       </c>
       <c r="E3" t="n">
-        <v>815</v>
+        <v>644</v>
       </c>
       <c r="F3" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G3" t="n">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>71.68000000000001</v>
+        <v>74.53</v>
       </c>
       <c r="J3" t="n">
-        <v>13.51</v>
+        <v>10.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>11.14</v>
+        <v>11.05</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -41304,7 +41433,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41315,31 +41444,31 @@
         <v>11545</v>
       </c>
       <c r="D4" t="n">
-        <v>7588</v>
+        <v>7930</v>
       </c>
       <c r="E4" t="n">
-        <v>1528</v>
+        <v>1186</v>
       </c>
       <c r="F4" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>65.73</v>
+        <v>68.69</v>
       </c>
       <c r="J4" t="n">
-        <v>13.24</v>
+        <v>10.27</v>
       </c>
       <c r="K4" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="L4" t="n">
-        <v>17.61</v>
+        <v>17.57</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M949"/>
+  <dimension ref="A1:M952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41261,6 +41261,135 @@
         <v>17.57</v>
       </c>
       <c r="M949" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D950" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E950" t="n">
+        <v>493</v>
+      </c>
+      <c r="F950" t="n">
+        <v>220</v>
+      </c>
+      <c r="G950" t="n">
+        <v>1546</v>
+      </c>
+      <c r="H950" t="n">
+        <v>668</v>
+      </c>
+      <c r="I950" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="J950" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="K950" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="L950" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="M950" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>6034</v>
+      </c>
+      <c r="D951" t="n">
+        <v>4555</v>
+      </c>
+      <c r="E951" t="n">
+        <v>579</v>
+      </c>
+      <c r="F951" t="n">
+        <v>199</v>
+      </c>
+      <c r="G951" t="n">
+        <v>664</v>
+      </c>
+      <c r="H951" t="n">
+        <v>37</v>
+      </c>
+      <c r="I951" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="J951" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K951" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L951" t="n">
+        <v>11</v>
+      </c>
+      <c r="M951" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>11545</v>
+      </c>
+      <c r="D952" t="n">
+        <v>8064</v>
+      </c>
+      <c r="E952" t="n">
+        <v>1039</v>
+      </c>
+      <c r="F952" t="n">
+        <v>420</v>
+      </c>
+      <c r="G952" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H952" t="n">
+        <v>0</v>
+      </c>
+      <c r="I952" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="J952" t="n">
+        <v>9</v>
+      </c>
+      <c r="K952" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="L952" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="M952" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41347,7 +41476,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41355,42 +41484,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5554</v>
+        <v>5555</v>
       </c>
       <c r="D2" t="n">
-        <v>2514</v>
+        <v>2628</v>
       </c>
       <c r="E2" t="n">
-        <v>619</v>
+        <v>493</v>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G2" t="n">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="H2" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>45.26</v>
+        <v>47.31</v>
       </c>
       <c r="J2" t="n">
-        <v>11.15</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>3.64</v>
+        <v>3.96</v>
       </c>
       <c r="L2" t="n">
-        <v>27.94</v>
+        <v>27.83</v>
       </c>
       <c r="M2" t="n">
-        <v>12.01</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41401,39 +41530,39 @@
         <v>6034</v>
       </c>
       <c r="D3" t="n">
-        <v>4497</v>
+        <v>4555</v>
       </c>
       <c r="E3" t="n">
-        <v>644</v>
+        <v>579</v>
       </c>
       <c r="F3" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="G3" t="n">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>74.53</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>10.67</v>
+        <v>9.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>11.05</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41444,31 +41573,31 @@
         <v>11545</v>
       </c>
       <c r="D4" t="n">
-        <v>7930</v>
+        <v>8064</v>
       </c>
       <c r="E4" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="G4" t="n">
-        <v>2029</v>
+        <v>2022</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.69</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>10.27</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="L4" t="n">
-        <v>17.57</v>
+        <v>17.51</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M952"/>
+  <dimension ref="A1:M955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41390,6 +41390,135 @@
         <v>17.51</v>
       </c>
       <c r="M952" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D953" t="n">
+        <v>2711</v>
+      </c>
+      <c r="E953" t="n">
+        <v>407</v>
+      </c>
+      <c r="F953" t="n">
+        <v>217</v>
+      </c>
+      <c r="G953" t="n">
+        <v>1551</v>
+      </c>
+      <c r="H953" t="n">
+        <v>668</v>
+      </c>
+      <c r="I953" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="J953" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="K953" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L953" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="M953" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>6035</v>
+      </c>
+      <c r="D954" t="n">
+        <v>4487</v>
+      </c>
+      <c r="E954" t="n">
+        <v>655</v>
+      </c>
+      <c r="F954" t="n">
+        <v>189</v>
+      </c>
+      <c r="G954" t="n">
+        <v>667</v>
+      </c>
+      <c r="H954" t="n">
+        <v>37</v>
+      </c>
+      <c r="I954" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="J954" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="K954" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L954" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="M954" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>11545</v>
+      </c>
+      <c r="D955" t="n">
+        <v>8062</v>
+      </c>
+      <c r="E955" t="n">
+        <v>1047</v>
+      </c>
+      <c r="F955" t="n">
+        <v>409</v>
+      </c>
+      <c r="G955" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H955" t="n">
+        <v>0</v>
+      </c>
+      <c r="I955" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="J955" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="K955" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="L955" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="M955" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41476,7 +41605,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41484,34 +41613,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5555</v>
+        <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2628</v>
+        <v>2711</v>
       </c>
       <c r="E2" t="n">
-        <v>493</v>
+        <v>407</v>
       </c>
       <c r="F2" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G2" t="n">
-        <v>1546</v>
+        <v>1551</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>47.31</v>
+        <v>48.81</v>
       </c>
       <c r="J2" t="n">
-        <v>8.869999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="K2" t="n">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="L2" t="n">
-        <v>27.83</v>
+        <v>27.93</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -41519,7 +41648,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41527,34 +41656,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="D3" t="n">
-        <v>4555</v>
+        <v>4487</v>
       </c>
       <c r="E3" t="n">
-        <v>579</v>
+        <v>655</v>
       </c>
       <c r="F3" t="n">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="G3" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H3" t="n">
         <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>75.48999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>9.6</v>
+        <v>10.85</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="M3" t="n">
         <v>0.61</v>
@@ -41562,7 +41691,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41573,31 +41702,31 @@
         <v>11545</v>
       </c>
       <c r="D4" t="n">
-        <v>8064</v>
+        <v>8062</v>
       </c>
       <c r="E4" t="n">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="F4" t="n">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="G4" t="n">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.84999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="L4" t="n">
-        <v>17.51</v>
+        <v>17.56</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M955"/>
+  <dimension ref="A1:M958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41519,6 +41519,135 @@
         <v>17.56</v>
       </c>
       <c r="M955" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D956" t="n">
+        <v>2692</v>
+      </c>
+      <c r="E956" t="n">
+        <v>409</v>
+      </c>
+      <c r="F956" t="n">
+        <v>230</v>
+      </c>
+      <c r="G956" t="n">
+        <v>1555</v>
+      </c>
+      <c r="H956" t="n">
+        <v>668</v>
+      </c>
+      <c r="I956" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="J956" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="K956" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L956" t="n">
+        <v>28</v>
+      </c>
+      <c r="M956" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>6035</v>
+      </c>
+      <c r="D957" t="n">
+        <v>4370</v>
+      </c>
+      <c r="E957" t="n">
+        <v>763</v>
+      </c>
+      <c r="F957" t="n">
+        <v>183</v>
+      </c>
+      <c r="G957" t="n">
+        <v>683</v>
+      </c>
+      <c r="H957" t="n">
+        <v>36</v>
+      </c>
+      <c r="I957" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="J957" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="K957" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L957" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="M957" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>11546</v>
+      </c>
+      <c r="D958" t="n">
+        <v>7938</v>
+      </c>
+      <c r="E958" t="n">
+        <v>1147</v>
+      </c>
+      <c r="F958" t="n">
+        <v>420</v>
+      </c>
+      <c r="G958" t="n">
+        <v>2041</v>
+      </c>
+      <c r="H958" t="n">
+        <v>0</v>
+      </c>
+      <c r="I958" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="J958" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="K958" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="L958" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="M958" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41605,7 +41734,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41616,31 +41745,31 @@
         <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2711</v>
+        <v>2692</v>
       </c>
       <c r="E2" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F2" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="G2" t="n">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>48.81</v>
+        <v>48.47</v>
       </c>
       <c r="J2" t="n">
-        <v>7.33</v>
+        <v>7.36</v>
       </c>
       <c r="K2" t="n">
-        <v>3.91</v>
+        <v>4.14</v>
       </c>
       <c r="L2" t="n">
-        <v>27.93</v>
+        <v>28</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -41648,7 +41777,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41659,39 +41788,39 @@
         <v>6035</v>
       </c>
       <c r="D3" t="n">
-        <v>4487</v>
+        <v>4370</v>
       </c>
       <c r="E3" t="n">
-        <v>655</v>
+        <v>763</v>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G3" t="n">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>74.34999999999999</v>
+        <v>72.41</v>
       </c>
       <c r="J3" t="n">
-        <v>10.85</v>
+        <v>12.64</v>
       </c>
       <c r="K3" t="n">
-        <v>3.13</v>
+        <v>3.03</v>
       </c>
       <c r="L3" t="n">
-        <v>11.05</v>
+        <v>11.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41699,34 +41828,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11545</v>
+        <v>11546</v>
       </c>
       <c r="D4" t="n">
-        <v>8062</v>
+        <v>7938</v>
       </c>
       <c r="E4" t="n">
-        <v>1047</v>
+        <v>1147</v>
       </c>
       <c r="F4" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="G4" t="n">
-        <v>2027</v>
+        <v>2041</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.83</v>
+        <v>68.75</v>
       </c>
       <c r="J4" t="n">
-        <v>9.07</v>
+        <v>9.93</v>
       </c>
       <c r="K4" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="L4" t="n">
-        <v>17.56</v>
+        <v>17.68</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M958"/>
+  <dimension ref="A1:M961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41648,6 +41648,135 @@
         <v>17.68</v>
       </c>
       <c r="M958" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D959" t="n">
+        <v>2664</v>
+      </c>
+      <c r="E959" t="n">
+        <v>429</v>
+      </c>
+      <c r="F959" t="n">
+        <v>233</v>
+      </c>
+      <c r="G959" t="n">
+        <v>1560</v>
+      </c>
+      <c r="H959" t="n">
+        <v>668</v>
+      </c>
+      <c r="I959" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="J959" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="K959" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L959" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="M959" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>6031</v>
+      </c>
+      <c r="D960" t="n">
+        <v>4274</v>
+      </c>
+      <c r="E960" t="n">
+        <v>852</v>
+      </c>
+      <c r="F960" t="n">
+        <v>176</v>
+      </c>
+      <c r="G960" t="n">
+        <v>691</v>
+      </c>
+      <c r="H960" t="n">
+        <v>38</v>
+      </c>
+      <c r="I960" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="J960" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="K960" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L960" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="M960" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D961" t="n">
+        <v>7814</v>
+      </c>
+      <c r="E961" t="n">
+        <v>1255</v>
+      </c>
+      <c r="F961" t="n">
+        <v>410</v>
+      </c>
+      <c r="G961" t="n">
+        <v>2061</v>
+      </c>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="J961" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="K961" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L961" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="M961" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41734,7 +41863,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41745,31 +41874,31 @@
         <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2692</v>
+        <v>2664</v>
       </c>
       <c r="E2" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G2" t="n">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>48.47</v>
+        <v>47.97</v>
       </c>
       <c r="J2" t="n">
-        <v>7.36</v>
+        <v>7.72</v>
       </c>
       <c r="K2" t="n">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>28.09</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -41777,7 +41906,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41785,42 +41914,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6035</v>
+        <v>6031</v>
       </c>
       <c r="D3" t="n">
-        <v>4370</v>
+        <v>4274</v>
       </c>
       <c r="E3" t="n">
-        <v>763</v>
+        <v>852</v>
       </c>
       <c r="F3" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G3" t="n">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>72.41</v>
+        <v>70.87</v>
       </c>
       <c r="J3" t="n">
-        <v>12.64</v>
+        <v>14.13</v>
       </c>
       <c r="K3" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="L3" t="n">
-        <v>11.32</v>
+        <v>11.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41828,34 +41957,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11546</v>
+        <v>11540</v>
       </c>
       <c r="D4" t="n">
-        <v>7938</v>
+        <v>7814</v>
       </c>
       <c r="E4" t="n">
-        <v>1147</v>
+        <v>1255</v>
       </c>
       <c r="F4" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G4" t="n">
-        <v>2041</v>
+        <v>2061</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.75</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.93</v>
+        <v>10.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>17.68</v>
+        <v>17.86</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M961"/>
+  <dimension ref="A1:M964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41777,6 +41777,135 @@
         <v>17.86</v>
       </c>
       <c r="M961" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D962" t="n">
+        <v>2558</v>
+      </c>
+      <c r="E962" t="n">
+        <v>532</v>
+      </c>
+      <c r="F962" t="n">
+        <v>228</v>
+      </c>
+      <c r="G962" t="n">
+        <v>1568</v>
+      </c>
+      <c r="H962" t="n">
+        <v>668</v>
+      </c>
+      <c r="I962" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="J962" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="K962" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L962" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="M962" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>6031</v>
+      </c>
+      <c r="D963" t="n">
+        <v>4205</v>
+      </c>
+      <c r="E963" t="n">
+        <v>907</v>
+      </c>
+      <c r="F963" t="n">
+        <v>178</v>
+      </c>
+      <c r="G963" t="n">
+        <v>703</v>
+      </c>
+      <c r="H963" t="n">
+        <v>38</v>
+      </c>
+      <c r="I963" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="J963" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="K963" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L963" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="M963" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D964" t="n">
+        <v>7665</v>
+      </c>
+      <c r="E964" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F964" t="n">
+        <v>406</v>
+      </c>
+      <c r="G964" t="n">
+        <v>2082</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="J964" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="K964" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L964" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="M964" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41863,7 +41992,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -41874,31 +42003,31 @@
         <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2664</v>
+        <v>2558</v>
       </c>
       <c r="E2" t="n">
-        <v>429</v>
+        <v>532</v>
       </c>
       <c r="F2" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G2" t="n">
-        <v>1560</v>
+        <v>1568</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>47.97</v>
+        <v>46.06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.72</v>
+        <v>9.58</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="L2" t="n">
-        <v>28.09</v>
+        <v>28.23</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -41906,7 +42035,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -41917,31 +42046,31 @@
         <v>6031</v>
       </c>
       <c r="D3" t="n">
-        <v>4274</v>
+        <v>4205</v>
       </c>
       <c r="E3" t="n">
-        <v>852</v>
+        <v>907</v>
       </c>
       <c r="F3" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G3" t="n">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>70.87</v>
+        <v>69.72</v>
       </c>
       <c r="J3" t="n">
-        <v>14.13</v>
+        <v>15.04</v>
       </c>
       <c r="K3" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="L3" t="n">
-        <v>11.46</v>
+        <v>11.66</v>
       </c>
       <c r="M3" t="n">
         <v>0.63</v>
@@ -41949,7 +42078,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -41960,31 +42089,31 @@
         <v>11540</v>
       </c>
       <c r="D4" t="n">
-        <v>7814</v>
+        <v>7665</v>
       </c>
       <c r="E4" t="n">
-        <v>1255</v>
+        <v>1387</v>
       </c>
       <c r="F4" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G4" t="n">
-        <v>2061</v>
+        <v>2082</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>67.70999999999999</v>
+        <v>66.42</v>
       </c>
       <c r="J4" t="n">
-        <v>10.88</v>
+        <v>12.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="L4" t="n">
-        <v>17.86</v>
+        <v>18.04</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M964"/>
+  <dimension ref="A1:M967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41906,6 +41906,135 @@
         <v>18.04</v>
       </c>
       <c r="M964" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>5554</v>
+      </c>
+      <c r="D965" t="n">
+        <v>2488</v>
+      </c>
+      <c r="E965" t="n">
+        <v>604</v>
+      </c>
+      <c r="F965" t="n">
+        <v>232</v>
+      </c>
+      <c r="G965" t="n">
+        <v>1562</v>
+      </c>
+      <c r="H965" t="n">
+        <v>668</v>
+      </c>
+      <c r="I965" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J965" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="K965" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L965" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="M965" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>6031</v>
+      </c>
+      <c r="D966" t="n">
+        <v>4273</v>
+      </c>
+      <c r="E966" t="n">
+        <v>843</v>
+      </c>
+      <c r="F966" t="n">
+        <v>175</v>
+      </c>
+      <c r="G966" t="n">
+        <v>702</v>
+      </c>
+      <c r="H966" t="n">
+        <v>38</v>
+      </c>
+      <c r="I966" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="J966" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="K966" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L966" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="M966" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D967" t="n">
+        <v>7656</v>
+      </c>
+      <c r="E967" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F967" t="n">
+        <v>403</v>
+      </c>
+      <c r="G967" t="n">
+        <v>2081</v>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="J967" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="K967" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="L967" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="M967" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41992,7 +42121,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -42003,31 +42132,31 @@
         <v>5554</v>
       </c>
       <c r="D2" t="n">
-        <v>2558</v>
+        <v>2488</v>
       </c>
       <c r="E2" t="n">
-        <v>532</v>
+        <v>604</v>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>46.06</v>
+        <v>44.8</v>
       </c>
       <c r="J2" t="n">
-        <v>9.58</v>
+        <v>10.88</v>
       </c>
       <c r="K2" t="n">
-        <v>4.11</v>
+        <v>4.18</v>
       </c>
       <c r="L2" t="n">
-        <v>28.23</v>
+        <v>28.12</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -42035,7 +42164,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -42046,31 +42175,31 @@
         <v>6031</v>
       </c>
       <c r="D3" t="n">
-        <v>4205</v>
+        <v>4273</v>
       </c>
       <c r="E3" t="n">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="F3" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G3" t="n">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>69.72</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>15.04</v>
+        <v>13.98</v>
       </c>
       <c r="K3" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>11.66</v>
+        <v>11.64</v>
       </c>
       <c r="M3" t="n">
         <v>0.63</v>
@@ -42078,7 +42207,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -42089,31 +42218,31 @@
         <v>11540</v>
       </c>
       <c r="D4" t="n">
-        <v>7665</v>
+        <v>7656</v>
       </c>
       <c r="E4" t="n">
-        <v>1387</v>
+        <v>1400</v>
       </c>
       <c r="F4" t="n">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G4" t="n">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>66.42</v>
+        <v>66.34</v>
       </c>
       <c r="J4" t="n">
-        <v>12.02</v>
+        <v>12.13</v>
       </c>
       <c r="K4" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="L4" t="n">
-        <v>18.04</v>
+        <v>18.03</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M967"/>
+  <dimension ref="A1:M970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42035,6 +42035,135 @@
         <v>18.03</v>
       </c>
       <c r="M967" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>5553</v>
+      </c>
+      <c r="D968" t="n">
+        <v>2555</v>
+      </c>
+      <c r="E968" t="n">
+        <v>533</v>
+      </c>
+      <c r="F968" t="n">
+        <v>248</v>
+      </c>
+      <c r="G968" t="n">
+        <v>1549</v>
+      </c>
+      <c r="H968" t="n">
+        <v>668</v>
+      </c>
+      <c r="I968" t="n">
+        <v>46.01</v>
+      </c>
+      <c r="J968" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K968" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L968" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="M968" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>6030</v>
+      </c>
+      <c r="D969" t="n">
+        <v>4501</v>
+      </c>
+      <c r="E969" t="n">
+        <v>617</v>
+      </c>
+      <c r="F969" t="n">
+        <v>174</v>
+      </c>
+      <c r="G969" t="n">
+        <v>700</v>
+      </c>
+      <c r="H969" t="n">
+        <v>38</v>
+      </c>
+      <c r="I969" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="J969" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="K969" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L969" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="M969" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>11538</v>
+      </c>
+      <c r="D970" t="n">
+        <v>7934</v>
+      </c>
+      <c r="E970" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F970" t="n">
+        <v>418</v>
+      </c>
+      <c r="G970" t="n">
+        <v>2068</v>
+      </c>
+      <c r="H970" t="n">
+        <v>0</v>
+      </c>
+      <c r="I970" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="J970" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="K970" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="L970" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="M970" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42121,7 +42250,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -42129,34 +42258,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>2488</v>
+        <v>2555</v>
       </c>
       <c r="E2" t="n">
-        <v>604</v>
+        <v>533</v>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="G2" t="n">
-        <v>1562</v>
+        <v>1549</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>44.8</v>
+        <v>46.01</v>
       </c>
       <c r="J2" t="n">
-        <v>10.88</v>
+        <v>9.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.18</v>
+        <v>4.47</v>
       </c>
       <c r="L2" t="n">
-        <v>28.12</v>
+        <v>27.89</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -42164,7 +42293,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -42172,34 +42301,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="D3" t="n">
-        <v>4273</v>
+        <v>4501</v>
       </c>
       <c r="E3" t="n">
-        <v>843</v>
+        <v>617</v>
       </c>
       <c r="F3" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G3" t="n">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>70.84999999999999</v>
+        <v>74.64</v>
       </c>
       <c r="J3" t="n">
-        <v>13.98</v>
+        <v>10.23</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="L3" t="n">
-        <v>11.64</v>
+        <v>11.61</v>
       </c>
       <c r="M3" t="n">
         <v>0.63</v>
@@ -42207,7 +42336,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -42215,34 +42344,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11540</v>
+        <v>11538</v>
       </c>
       <c r="D4" t="n">
-        <v>7656</v>
+        <v>7934</v>
       </c>
       <c r="E4" t="n">
-        <v>1400</v>
+        <v>1118</v>
       </c>
       <c r="F4" t="n">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G4" t="n">
-        <v>2081</v>
+        <v>2068</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>66.34</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>12.13</v>
+        <v>9.69</v>
       </c>
       <c r="K4" t="n">
-        <v>3.49</v>
+        <v>3.62</v>
       </c>
       <c r="L4" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M970"/>
+  <dimension ref="A1:M973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42164,6 +42164,135 @@
         <v>17.92</v>
       </c>
       <c r="M970" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>5553</v>
+      </c>
+      <c r="D971" t="n">
+        <v>2657</v>
+      </c>
+      <c r="E971" t="n">
+        <v>436</v>
+      </c>
+      <c r="F971" t="n">
+        <v>256</v>
+      </c>
+      <c r="G971" t="n">
+        <v>1536</v>
+      </c>
+      <c r="H971" t="n">
+        <v>668</v>
+      </c>
+      <c r="I971" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="J971" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="K971" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="L971" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="M971" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>6032</v>
+      </c>
+      <c r="D972" t="n">
+        <v>4555</v>
+      </c>
+      <c r="E972" t="n">
+        <v>558</v>
+      </c>
+      <c r="F972" t="n">
+        <v>181</v>
+      </c>
+      <c r="G972" t="n">
+        <v>700</v>
+      </c>
+      <c r="H972" t="n">
+        <v>38</v>
+      </c>
+      <c r="I972" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="J972" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="K972" t="n">
+        <v>3</v>
+      </c>
+      <c r="L972" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M972" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>11540</v>
+      </c>
+      <c r="D973" t="n">
+        <v>8049</v>
+      </c>
+      <c r="E973" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F973" t="n">
+        <v>429</v>
+      </c>
+      <c r="G973" t="n">
+        <v>2062</v>
+      </c>
+      <c r="H973" t="n">
+        <v>0</v>
+      </c>
+      <c r="I973" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="J973" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="K973" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="L973" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="M973" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42250,7 +42379,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -42261,31 +42390,31 @@
         <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>2555</v>
+        <v>2657</v>
       </c>
       <c r="E2" t="n">
-        <v>533</v>
+        <v>436</v>
       </c>
       <c r="F2" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G2" t="n">
-        <v>1549</v>
+        <v>1536</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>46.01</v>
+        <v>47.85</v>
       </c>
       <c r="J2" t="n">
-        <v>9.6</v>
+        <v>7.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="L2" t="n">
-        <v>27.89</v>
+        <v>27.66</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -42293,7 +42422,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -42301,16 +42430,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="D3" t="n">
-        <v>4501</v>
+        <v>4555</v>
       </c>
       <c r="E3" t="n">
-        <v>617</v>
+        <v>558</v>
       </c>
       <c r="F3" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
@@ -42319,16 +42448,16 @@
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>74.64</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>10.23</v>
+        <v>9.25</v>
       </c>
       <c r="K3" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>11.61</v>
+        <v>11.6</v>
       </c>
       <c r="M3" t="n">
         <v>0.63</v>
@@ -42336,7 +42465,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -42344,34 +42473,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11538</v>
+        <v>11540</v>
       </c>
       <c r="D4" t="n">
-        <v>7934</v>
+        <v>8049</v>
       </c>
       <c r="E4" t="n">
-        <v>1118</v>
+        <v>1000</v>
       </c>
       <c r="F4" t="n">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="G4" t="n">
-        <v>2068</v>
+        <v>2062</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>68.76000000000001</v>
+        <v>69.75</v>
       </c>
       <c r="J4" t="n">
-        <v>9.69</v>
+        <v>8.67</v>
       </c>
       <c r="K4" t="n">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="L4" t="n">
-        <v>17.92</v>
+        <v>17.87</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M973"/>
+  <dimension ref="A1:M976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42293,6 +42293,135 @@
         <v>17.87</v>
       </c>
       <c r="M973" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>5553</v>
+      </c>
+      <c r="D974" t="n">
+        <v>2677</v>
+      </c>
+      <c r="E974" t="n">
+        <v>426</v>
+      </c>
+      <c r="F974" t="n">
+        <v>243</v>
+      </c>
+      <c r="G974" t="n">
+        <v>1539</v>
+      </c>
+      <c r="H974" t="n">
+        <v>668</v>
+      </c>
+      <c r="I974" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="J974" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="K974" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="L974" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="M974" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>6032</v>
+      </c>
+      <c r="D975" t="n">
+        <v>4319</v>
+      </c>
+      <c r="E975" t="n">
+        <v>791</v>
+      </c>
+      <c r="F975" t="n">
+        <v>184</v>
+      </c>
+      <c r="G975" t="n">
+        <v>701</v>
+      </c>
+      <c r="H975" t="n">
+        <v>37</v>
+      </c>
+      <c r="I975" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="J975" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="K975" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L975" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="M975" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>11541</v>
+      </c>
+      <c r="D976" t="n">
+        <v>7827</v>
+      </c>
+      <c r="E976" t="n">
+        <v>1226</v>
+      </c>
+      <c r="F976" t="n">
+        <v>428</v>
+      </c>
+      <c r="G976" t="n">
+        <v>2060</v>
+      </c>
+      <c r="H976" t="n">
+        <v>0</v>
+      </c>
+      <c r="I976" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="J976" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="K976" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L976" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="M976" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42379,7 +42508,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -42390,31 +42519,31 @@
         <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>2657</v>
+        <v>2677</v>
       </c>
       <c r="E2" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="F2" t="n">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G2" t="n">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>47.85</v>
+        <v>48.21</v>
       </c>
       <c r="J2" t="n">
-        <v>7.85</v>
+        <v>7.67</v>
       </c>
       <c r="K2" t="n">
-        <v>4.61</v>
+        <v>4.38</v>
       </c>
       <c r="L2" t="n">
-        <v>27.66</v>
+        <v>27.71</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -42422,7 +42551,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -42433,39 +42562,39 @@
         <v>6032</v>
       </c>
       <c r="D3" t="n">
-        <v>4555</v>
+        <v>4319</v>
       </c>
       <c r="E3" t="n">
-        <v>558</v>
+        <v>791</v>
       </c>
       <c r="F3" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G3" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>75.51000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>9.25</v>
+        <v>13.11</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
       <c r="M3" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -42473,34 +42602,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11540</v>
+        <v>11541</v>
       </c>
       <c r="D4" t="n">
-        <v>8049</v>
+        <v>7827</v>
       </c>
       <c r="E4" t="n">
-        <v>1000</v>
+        <v>1226</v>
       </c>
       <c r="F4" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G4" t="n">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.75</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>8.67</v>
+        <v>10.62</v>
       </c>
       <c r="K4" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="L4" t="n">
-        <v>17.87</v>
+        <v>17.85</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M976"/>
+  <dimension ref="A1:M979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42422,6 +42422,135 @@
         <v>17.85</v>
       </c>
       <c r="M976" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>5553</v>
+      </c>
+      <c r="D977" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E977" t="n">
+        <v>422</v>
+      </c>
+      <c r="F977" t="n">
+        <v>238</v>
+      </c>
+      <c r="G977" t="n">
+        <v>1551</v>
+      </c>
+      <c r="H977" t="n">
+        <v>668</v>
+      </c>
+      <c r="I977" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="J977" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K977" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L977" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="M977" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>6031</v>
+      </c>
+      <c r="D978" t="n">
+        <v>4495</v>
+      </c>
+      <c r="E978" t="n">
+        <v>618</v>
+      </c>
+      <c r="F978" t="n">
+        <v>189</v>
+      </c>
+      <c r="G978" t="n">
+        <v>693</v>
+      </c>
+      <c r="H978" t="n">
+        <v>36</v>
+      </c>
+      <c r="I978" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="J978" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="K978" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L978" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="M978" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>11541</v>
+      </c>
+      <c r="D979" t="n">
+        <v>8025</v>
+      </c>
+      <c r="E979" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F979" t="n">
+        <v>423</v>
+      </c>
+      <c r="G979" t="n">
+        <v>2063</v>
+      </c>
+      <c r="H979" t="n">
+        <v>0</v>
+      </c>
+      <c r="I979" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="J979" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K979" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="L979" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="M979" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42508,7 +42637,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -42519,31 +42648,31 @@
         <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="E2" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F2" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G2" t="n">
-        <v>1539</v>
+        <v>1551</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>48.21</v>
+        <v>48.15</v>
       </c>
       <c r="J2" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="L2" t="n">
-        <v>27.71</v>
+        <v>27.93</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -42551,7 +42680,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -42559,42 +42688,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="D3" t="n">
-        <v>4319</v>
+        <v>4495</v>
       </c>
       <c r="E3" t="n">
-        <v>791</v>
+        <v>618</v>
       </c>
       <c r="F3" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G3" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>71.59999999999999</v>
+        <v>74.53</v>
       </c>
       <c r="J3" t="n">
-        <v>13.11</v>
+        <v>10.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="L3" t="n">
-        <v>11.62</v>
+        <v>11.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -42605,31 +42734,31 @@
         <v>11541</v>
       </c>
       <c r="D4" t="n">
-        <v>7827</v>
+        <v>8025</v>
       </c>
       <c r="E4" t="n">
-        <v>1226</v>
+        <v>1030</v>
       </c>
       <c r="F4" t="n">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G4" t="n">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>67.81999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="J4" t="n">
-        <v>10.62</v>
+        <v>8.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="L4" t="n">
-        <v>17.85</v>
+        <v>17.88</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>

--- a/data/historico_conectividad.xlsx
+++ b/data/historico_conectividad.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M979"/>
+  <dimension ref="A1:M982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42551,6 +42551,135 @@
         <v>17.88</v>
       </c>
       <c r="M979" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Telemetría</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>5553</v>
+      </c>
+      <c r="D980" t="n">
+        <v>2695</v>
+      </c>
+      <c r="E980" t="n">
+        <v>412</v>
+      </c>
+      <c r="F980" t="n">
+        <v>229</v>
+      </c>
+      <c r="G980" t="n">
+        <v>1549</v>
+      </c>
+      <c r="H980" t="n">
+        <v>668</v>
+      </c>
+      <c r="I980" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="J980" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="K980" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="L980" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="M980" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>GPS (según REGLA)</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>6032</v>
+      </c>
+      <c r="D981" t="n">
+        <v>4588</v>
+      </c>
+      <c r="E981" t="n">
+        <v>527</v>
+      </c>
+      <c r="F981" t="n">
+        <v>189</v>
+      </c>
+      <c r="G981" t="n">
+        <v>692</v>
+      </c>
+      <c r="H981" t="n">
+        <v>36</v>
+      </c>
+      <c r="I981" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="J981" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="K981" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L981" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="M981" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>GPS (todas con gps_timestamp)</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>11542</v>
+      </c>
+      <c r="D982" t="n">
+        <v>8131</v>
+      </c>
+      <c r="E982" t="n">
+        <v>935</v>
+      </c>
+      <c r="F982" t="n">
+        <v>410</v>
+      </c>
+      <c r="G982" t="n">
+        <v>2066</v>
+      </c>
+      <c r="H982" t="n">
+        <v>0</v>
+      </c>
+      <c r="I982" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="J982" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K982" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L982" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M982" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42637,7 +42766,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -42648,31 +42777,31 @@
         <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>2674</v>
+        <v>2695</v>
       </c>
       <c r="E2" t="n">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="F2" t="n">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H2" t="n">
         <v>668</v>
       </c>
       <c r="I2" t="n">
-        <v>48.15</v>
+        <v>48.53</v>
       </c>
       <c r="J2" t="n">
-        <v>7.6</v>
+        <v>7.42</v>
       </c>
       <c r="K2" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="L2" t="n">
-        <v>27.93</v>
+        <v>27.89</v>
       </c>
       <c r="M2" t="n">
         <v>12.03</v>
@@ -42680,7 +42809,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -42688,34 +42817,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="D3" t="n">
-        <v>4495</v>
+        <v>4588</v>
       </c>
       <c r="E3" t="n">
-        <v>618</v>
+        <v>527</v>
       </c>
       <c r="F3" t="n">
         <v>189</v>
       </c>
       <c r="G3" t="n">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H3" t="n">
         <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>74.53</v>
+        <v>76.06</v>
       </c>
       <c r="J3" t="n">
-        <v>10.25</v>
+        <v>8.74</v>
       </c>
       <c r="K3" t="n">
         <v>3.13</v>
       </c>
       <c r="L3" t="n">
-        <v>11.49</v>
+        <v>11.47</v>
       </c>
       <c r="M3" t="n">
         <v>0.6</v>
@@ -42723,7 +42852,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -42731,34 +42860,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11541</v>
+        <v>11542</v>
       </c>
       <c r="D4" t="n">
-        <v>8025</v>
+        <v>8131</v>
       </c>
       <c r="E4" t="n">
-        <v>1030</v>
+        <v>935</v>
       </c>
       <c r="F4" t="n">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="G4" t="n">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>69.53</v>
+        <v>70.45</v>
       </c>
       <c r="J4" t="n">
-        <v>8.92</v>
+        <v>8.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>17.88</v>
+        <v>17.9</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
